--- a/src/BACKUP/DER OPS NEW CRM 2023 (Only commo).xlsx
+++ b/src/BACKUP/DER OPS NEW CRM 2023 (Only commo).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\omimr\mon-crm\src\BACKUP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2A97D2F-CC9F-4B86-B660-57EE74C93F52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10E62927-4C1F-459E-B197-D1994B60797A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28935" yWindow="-135" windowWidth="29070" windowHeight="15750" xr2:uid="{D6CCACEF-1C1F-4D1F-866B-107900FEC4F4}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{D6CCACEF-1C1F-4D1F-866B-107900FEC4F4}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8842" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8846" uniqueCount="383">
   <si>
     <t>ref</t>
   </si>
@@ -1186,6 +1186,9 @@
   <si>
     <t>CBOT Soybean Meal Mar 2023</t>
   </si>
+  <si>
+    <t>C4359</t>
+  </si>
 </sst>
 </file>
 
@@ -1574,32 +1577,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25EABF89-24FB-4405-88E9-EEE94EEA1CFA}">
   <sheetPr codeName="Feuil1"/>
   <dimension ref="A1:T813"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.73046875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="6.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="45.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.3984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="45.3984375" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.1328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.86328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.3984375" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.86328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.73046875" style="2" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="41.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="39.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="10.7109375" style="2"/>
+    <col min="14" max="14" width="11.1328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="41.73046875" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="39.59765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.59765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.3984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.1328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="10.73046875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1661,7 +1664,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A2" s="2">
         <v>3899</v>
       </c>
@@ -1714,7 +1717,7 @@
         <v>61.44</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A3" s="2">
         <v>3898</v>
       </c>
@@ -1767,7 +1770,7 @@
         <v>56.32</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A4" s="2">
         <v>3893</v>
       </c>
@@ -1820,7 +1823,7 @@
         <v>35.840000000000003</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A5" s="2">
         <v>3892</v>
       </c>
@@ -1873,7 +1876,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A6" s="2">
         <v>3890</v>
       </c>
@@ -1926,7 +1929,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A7" s="2">
         <v>3886</v>
       </c>
@@ -1979,7 +1982,7 @@
         <v>403.92700000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A8" s="2">
         <v>3884</v>
       </c>
@@ -2032,7 +2035,7 @@
         <v>275.40499999999997</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A9" s="2">
         <v>3882</v>
       </c>
@@ -2085,7 +2088,7 @@
         <v>275.40499999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A10" s="2">
         <v>3880</v>
       </c>
@@ -2138,7 +2141,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A11" s="2">
         <v>3879</v>
       </c>
@@ -2191,7 +2194,7 @@
         <v>91.802000000000007</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A12" s="2">
         <v>3878</v>
       </c>
@@ -2244,7 +2247,7 @@
         <v>284.58499999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A13" s="2">
         <v>3877</v>
       </c>
@@ -2297,7 +2300,7 @@
         <v>183.60300000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A14" s="2">
         <v>3876</v>
       </c>
@@ -2350,7 +2353,7 @@
         <v>91.802000000000007</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A15" s="2">
         <v>3875</v>
       </c>
@@ -2403,7 +2406,7 @@
         <v>91.802000000000007</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A16" s="2">
         <v>3873</v>
       </c>
@@ -2456,7 +2459,7 @@
         <v>61.44</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A17" s="2">
         <v>3872</v>
       </c>
@@ -2509,7 +2512,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A18" s="2">
         <v>3868</v>
       </c>
@@ -2562,7 +2565,7 @@
         <v>45.524999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A19" s="2">
         <v>3896</v>
       </c>
@@ -2615,7 +2618,7 @@
         <v>91.05</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A20" s="2">
         <v>3895</v>
       </c>
@@ -2668,7 +2671,7 @@
         <v>5.12</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A21" s="2">
         <v>3871</v>
       </c>
@@ -2721,7 +2724,7 @@
         <v>154.785</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A22" s="2">
         <v>3869</v>
       </c>
@@ -2774,7 +2777,7 @@
         <v>209.41499999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A23" s="2">
         <v>3867</v>
       </c>
@@ -2827,7 +2830,7 @@
         <v>148.47999999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A24" s="2">
         <v>3865</v>
       </c>
@@ -2880,7 +2883,7 @@
         <v>56.32</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A25" s="2">
         <v>3864</v>
       </c>
@@ -2933,7 +2936,7 @@
         <v>45.36</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A26" s="2">
         <v>3860</v>
       </c>
@@ -2986,7 +2989,7 @@
         <v>10.24</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A27" s="2">
         <v>3859</v>
       </c>
@@ -3039,7 +3042,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A28" s="2">
         <v>3856</v>
       </c>
@@ -3092,7 +3095,7 @@
         <v>45.198999999999998</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A29" s="2">
         <v>3852</v>
       </c>
@@ -3145,7 +3148,7 @@
         <v>135.81899999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A30" s="2">
         <v>3850</v>
       </c>
@@ -3198,7 +3201,7 @@
         <v>1358.192</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A31" s="2">
         <v>3848</v>
       </c>
@@ -3251,7 +3254,7 @@
         <v>271.63799999999998</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A32" s="2">
         <v>3846</v>
       </c>
@@ -3298,7 +3301,7 @@
         <v>102.4</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A33" s="2">
         <v>3845</v>
       </c>
@@ -3345,7 +3348,7 @@
         <v>102.4</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A34" s="2">
         <v>3844</v>
       </c>
@@ -3392,7 +3395,7 @@
         <v>102.4</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A35" s="2">
         <v>3843</v>
       </c>
@@ -3439,7 +3442,7 @@
         <v>102.4</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A36" s="2">
         <v>3839</v>
       </c>
@@ -3492,7 +3495,7 @@
         <v>265.62299999999999</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A37" s="2">
         <v>3837</v>
       </c>
@@ -3539,7 +3542,7 @@
         <v>711.82799999999997</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A38" s="2">
         <v>3835</v>
       </c>
@@ -3592,7 +3595,7 @@
         <v>4448.9260000000004</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A39" s="2">
         <v>3832</v>
       </c>
@@ -3645,7 +3648,7 @@
         <v>122.88</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A40" s="2">
         <v>3830</v>
       </c>
@@ -3698,7 +3701,7 @@
         <v>20.48</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A41" s="2">
         <v>3829</v>
       </c>
@@ -3751,7 +3754,7 @@
         <v>5.12</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A42" s="2">
         <v>3827</v>
       </c>
@@ -3804,7 +3807,7 @@
         <v>1089.1600000000001</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A43" s="2">
         <v>3824</v>
       </c>
@@ -3857,7 +3860,7 @@
         <v>46.08</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A44" s="2">
         <v>3823</v>
       </c>
@@ -3910,7 +3913,7 @@
         <v>430.08</v>
       </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A45" s="2">
         <v>3822</v>
       </c>
@@ -3963,7 +3966,7 @@
         <v>620.92100000000005</v>
       </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A46" s="2">
         <v>3819</v>
       </c>
@@ -4016,7 +4019,7 @@
         <v>238.733</v>
       </c>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A47" s="2">
         <v>3818</v>
       </c>
@@ -4069,7 +4072,7 @@
         <v>114.946</v>
       </c>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A48" s="2">
         <v>3816</v>
       </c>
@@ -4122,7 +4125,7 @@
         <v>20.48</v>
       </c>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A49" s="2">
         <v>3813</v>
       </c>
@@ -4175,7 +4178,7 @@
         <v>442.09800000000001</v>
       </c>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A50" s="2">
         <v>3812</v>
       </c>
@@ -4228,7 +4231,7 @@
         <v>2210.491</v>
       </c>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A51" s="2">
         <v>3809</v>
       </c>
@@ -4281,7 +4284,7 @@
         <v>88.29</v>
       </c>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A52" s="2">
         <v>3808</v>
       </c>
@@ -4328,7 +4331,7 @@
         <v>176.58</v>
       </c>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A53" s="2">
         <v>3807</v>
       </c>
@@ -4381,7 +4384,7 @@
         <v>353.16</v>
       </c>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A54" s="2">
         <v>3806</v>
       </c>
@@ -4428,7 +4431,7 @@
         <v>44.145000000000003</v>
       </c>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A55" s="2">
         <v>3805</v>
       </c>
@@ -4475,7 +4478,7 @@
         <v>88.29</v>
       </c>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A56" s="2">
         <v>3803</v>
       </c>
@@ -4522,7 +4525,7 @@
         <v>44.145000000000003</v>
       </c>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A57" s="2">
         <v>3802</v>
       </c>
@@ -4575,7 +4578,7 @@
         <v>882.9</v>
       </c>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A58" s="2">
         <v>3801</v>
       </c>
@@ -4628,7 +4631,7 @@
         <v>353.16</v>
       </c>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A59" s="2">
         <v>3798</v>
       </c>
@@ -4681,7 +4684,7 @@
         <v>882.9</v>
       </c>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A60" s="2">
         <v>3797</v>
       </c>
@@ -4734,7 +4737,7 @@
         <v>441.89600000000002</v>
       </c>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A61" s="2">
         <v>3796</v>
       </c>
@@ -4781,7 +4784,7 @@
         <v>176.75800000000001</v>
       </c>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A62" s="2">
         <v>3795</v>
       </c>
@@ -4828,7 +4831,7 @@
         <v>176.75800000000001</v>
       </c>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A63" s="2">
         <v>3794</v>
       </c>
@@ -4875,7 +4878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A64" s="2">
         <v>3793</v>
       </c>
@@ -4922,7 +4925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A65" s="2">
         <v>3792</v>
       </c>
@@ -4969,7 +4972,7 @@
         <v>260.71800000000002</v>
       </c>
     </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A66" s="2">
         <v>3785</v>
       </c>
@@ -5016,7 +5019,7 @@
         <v>621.149</v>
       </c>
     </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A67" s="2">
         <v>3787</v>
       </c>
@@ -5069,7 +5072,7 @@
         <v>5.12</v>
       </c>
     </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A68" s="2">
         <v>3786</v>
       </c>
@@ -5122,7 +5125,7 @@
         <v>442.584</v>
       </c>
     </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A69" s="2">
         <v>3784</v>
       </c>
@@ -5169,7 +5172,7 @@
         <v>261.12400000000002</v>
       </c>
     </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A70" s="2">
         <v>3782</v>
       </c>
@@ -5222,7 +5225,7 @@
         <v>88.516999999999996</v>
       </c>
     </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A71" s="2">
         <v>3780</v>
       </c>
@@ -5275,7 +5278,7 @@
         <v>20.48</v>
       </c>
     </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A72" s="2">
         <v>3779</v>
       </c>
@@ -5328,7 +5331,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A73" s="2">
         <v>3777</v>
       </c>
@@ -5381,7 +5384,7 @@
         <v>30.72</v>
       </c>
     </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A74" s="2">
         <v>3775</v>
       </c>
@@ -5434,7 +5437,7 @@
         <v>88.063000000000002</v>
       </c>
     </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A75" s="2">
         <v>3772</v>
       </c>
@@ -5487,7 +5490,7 @@
         <v>219.69200000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A76" s="2">
         <v>3771</v>
       </c>
@@ -5540,7 +5543,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A77" s="2">
         <v>3770</v>
       </c>
@@ -5593,7 +5596,7 @@
         <v>527.26099999999997</v>
       </c>
     </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A78" s="2">
         <v>3769</v>
       </c>
@@ -5646,7 +5649,7 @@
         <v>175.75399999999999</v>
       </c>
     </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A79" s="2">
         <v>3768</v>
       </c>
@@ -5699,7 +5702,7 @@
         <v>43.938000000000002</v>
       </c>
     </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A80" s="2">
         <v>3766</v>
       </c>
@@ -5752,7 +5755,7 @@
         <v>263.63099999999997</v>
       </c>
     </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A81" s="2">
         <v>3773</v>
       </c>
@@ -5805,7 +5808,7 @@
         <v>264.09300000000002</v>
       </c>
     </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A82" s="2">
         <v>3765</v>
       </c>
@@ -5852,7 +5855,7 @@
         <v>616.21600000000001</v>
       </c>
     </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A83" s="2">
         <v>3763</v>
       </c>
@@ -5905,7 +5908,7 @@
         <v>88.031000000000006</v>
       </c>
     </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A84" s="2">
         <v>3761</v>
       </c>
@@ -5958,7 +5961,7 @@
         <v>880.30799999999999</v>
       </c>
     </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A85" s="2">
         <v>3759</v>
       </c>
@@ -6011,7 +6014,7 @@
         <v>2960.7249999999999</v>
       </c>
     </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A86" s="2">
         <v>3757</v>
       </c>
@@ -6064,7 +6067,7 @@
         <v>88.031000000000006</v>
       </c>
     </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A87" s="2">
         <v>3755</v>
       </c>
@@ -6117,7 +6120,7 @@
         <v>173.72900000000001</v>
       </c>
     </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A88" s="2">
         <v>3753</v>
       </c>
@@ -6170,7 +6173,7 @@
         <v>2942.31</v>
       </c>
     </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A89" s="2">
         <v>3746</v>
       </c>
@@ -6223,7 +6226,7 @@
         <v>864.27</v>
       </c>
     </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A90" s="2">
         <v>3745</v>
       </c>
@@ -6276,7 +6279,7 @@
         <v>3889.2159999999999</v>
       </c>
     </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A91" s="2">
         <v>3743</v>
       </c>
@@ -6329,7 +6332,7 @@
         <v>1728.54</v>
       </c>
     </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A92" s="2">
         <v>3741</v>
       </c>
@@ -6382,7 +6385,7 @@
         <v>1296.405</v>
       </c>
     </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A93" s="2">
         <v>3738</v>
       </c>
@@ -6435,7 +6438,7 @@
         <v>20.48</v>
       </c>
     </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A94" s="2">
         <v>3735</v>
       </c>
@@ -6488,7 +6491,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A95" s="2">
         <v>3734</v>
       </c>
@@ -6541,7 +6544,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A96" s="2">
         <v>3732</v>
       </c>
@@ -6594,7 +6597,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A97" s="2">
         <v>3730</v>
       </c>
@@ -6647,7 +6650,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A98" s="2">
         <v>3729</v>
       </c>
@@ -6700,7 +6703,7 @@
         <v>86.596999999999994</v>
       </c>
     </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A99" s="2">
         <v>3727</v>
       </c>
@@ -6753,7 +6756,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A100" s="2">
         <v>3725</v>
       </c>
@@ -6806,7 +6809,7 @@
         <v>15.36</v>
       </c>
     </row>
-    <row r="101" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A101" s="2">
         <v>3724</v>
       </c>
@@ -6859,7 +6862,7 @@
         <v>870.02099999999996</v>
       </c>
     </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A102" s="2">
         <v>3723</v>
       </c>
@@ -6912,7 +6915,7 @@
         <v>87.001999999999995</v>
       </c>
     </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A103" s="2">
         <v>3722</v>
       </c>
@@ -6965,7 +6968,7 @@
         <v>87.001999999999995</v>
       </c>
     </row>
-    <row r="104" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A104" s="2">
         <v>3721</v>
       </c>
@@ -7018,7 +7021,7 @@
         <v>87.001999999999995</v>
       </c>
     </row>
-    <row r="105" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A105" s="2">
         <v>3719</v>
       </c>
@@ -7071,7 +7074,7 @@
         <v>5.12</v>
       </c>
     </row>
-    <row r="106" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A106" s="2">
         <v>3717</v>
       </c>
@@ -7124,7 +7127,7 @@
         <v>40.96</v>
       </c>
     </row>
-    <row r="107" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A107" s="2">
         <v>3714</v>
       </c>
@@ -7177,7 +7180,7 @@
         <v>257.702</v>
       </c>
     </row>
-    <row r="108" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A108" s="2">
         <v>3712</v>
       </c>
@@ -7230,7 +7233,7 @@
         <v>193.27600000000001</v>
       </c>
     </row>
-    <row r="109" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A109" s="2">
         <v>3709</v>
       </c>
@@ -7283,7 +7286,7 @@
         <v>192.11</v>
       </c>
     </row>
-    <row r="110" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A110" s="2">
         <v>3708</v>
       </c>
@@ -7336,7 +7339,7 @@
         <v>234.80099999999999</v>
       </c>
     </row>
-    <row r="111" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A111" s="2">
         <v>3707</v>
       </c>
@@ -7389,7 +7392,7 @@
         <v>64.037000000000006</v>
       </c>
     </row>
-    <row r="112" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A112" s="2">
         <v>3704</v>
       </c>
@@ -7442,7 +7445,7 @@
         <v>341.49599999999998</v>
       </c>
     </row>
-    <row r="113" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A113" s="2">
         <v>3703</v>
       </c>
@@ -7495,7 +7498,7 @@
         <v>85.373999999999995</v>
       </c>
     </row>
-    <row r="114" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A114" s="2">
         <v>3699</v>
       </c>
@@ -7548,7 +7551,7 @@
         <v>21.416</v>
       </c>
     </row>
-    <row r="115" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A115" s="2">
         <v>3698</v>
       </c>
@@ -7601,7 +7604,7 @@
         <v>21.416</v>
       </c>
     </row>
-    <row r="116" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A116" s="2">
         <v>3685</v>
       </c>
@@ -7654,7 +7657,7 @@
         <v>599.65899999999999</v>
       </c>
     </row>
-    <row r="117" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A117" s="2">
         <v>3684</v>
       </c>
@@ -7707,7 +7710,7 @@
         <v>599.65899999999999</v>
       </c>
     </row>
-    <row r="118" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A118" s="2">
         <v>3683</v>
       </c>
@@ -7760,7 +7763,7 @@
         <v>42.832999999999998</v>
       </c>
     </row>
-    <row r="119" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A119" s="2">
         <v>3682</v>
       </c>
@@ -7813,7 +7816,7 @@
         <v>42.832999999999998</v>
       </c>
     </row>
-    <row r="120" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A120" s="2">
         <v>3680</v>
       </c>
@@ -7866,7 +7869,7 @@
         <v>188.464</v>
       </c>
     </row>
-    <row r="121" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A121" s="2">
         <v>3678</v>
       </c>
@@ -7919,7 +7922,7 @@
         <v>25.7</v>
       </c>
     </row>
-    <row r="122" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A122" s="2">
         <v>3674</v>
       </c>
@@ -7972,7 +7975,7 @@
         <v>171.33099999999999</v>
       </c>
     </row>
-    <row r="123" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A123" s="2">
         <v>3673</v>
       </c>
@@ -8025,7 +8028,7 @@
         <v>85.665999999999997</v>
       </c>
     </row>
-    <row r="124" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A124" s="2">
         <v>3672</v>
       </c>
@@ -8078,7 +8081,7 @@
         <v>171.33099999999999</v>
       </c>
     </row>
-    <row r="125" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A125" s="2">
         <v>3670</v>
       </c>
@@ -8131,7 +8134,7 @@
         <v>256.99700000000001</v>
       </c>
     </row>
-    <row r="126" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A126" s="2">
         <v>3668</v>
       </c>
@@ -8184,7 +8187,7 @@
         <v>42.832999999999998</v>
       </c>
     </row>
-    <row r="127" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A127" s="2">
         <v>3667</v>
       </c>
@@ -8237,7 +8240,7 @@
         <v>128.49799999999999</v>
       </c>
     </row>
-    <row r="128" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A128" s="2">
         <v>3666</v>
       </c>
@@ -8290,7 +8293,7 @@
         <v>42.832999999999998</v>
       </c>
     </row>
-    <row r="129" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A129" s="2">
         <v>3664</v>
       </c>
@@ -8343,7 +8346,7 @@
         <v>428.32799999999997</v>
       </c>
     </row>
-    <row r="130" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A130" s="2">
         <v>3662</v>
       </c>
@@ -8396,7 +8399,7 @@
         <v>688.95299999999997</v>
       </c>
     </row>
-    <row r="131" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A131" s="2">
         <v>3659</v>
       </c>
@@ -8449,7 +8452,7 @@
         <v>129.179</v>
       </c>
     </row>
-    <row r="132" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A132" s="2">
         <v>3658</v>
       </c>
@@ -8502,7 +8505,7 @@
         <v>43.06</v>
       </c>
     </row>
-    <row r="133" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A133" s="2">
         <v>3656</v>
       </c>
@@ -8555,7 +8558,7 @@
         <v>86.119</v>
       </c>
     </row>
-    <row r="134" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A134" s="2">
         <v>3655</v>
       </c>
@@ -8602,7 +8605,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="135" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A135" s="2">
         <v>3654</v>
       </c>
@@ -8649,7 +8652,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="136" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A136" s="2">
         <v>3651</v>
       </c>
@@ -8702,7 +8705,7 @@
         <v>855.76499999999999</v>
       </c>
     </row>
-    <row r="137" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A137" s="2">
         <v>3650</v>
       </c>
@@ -8755,7 +8758,7 @@
         <v>1283.6469999999999</v>
       </c>
     </row>
-    <row r="138" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A138" s="2">
         <v>3648</v>
       </c>
@@ -8808,7 +8811,7 @@
         <v>2557.3319999999999</v>
       </c>
     </row>
-    <row r="139" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A139" s="2">
         <v>3643</v>
       </c>
@@ -8861,7 +8864,7 @@
         <v>430.07</v>
       </c>
     </row>
-    <row r="140" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A140" s="2">
         <v>3642</v>
       </c>
@@ -8914,7 +8917,7 @@
         <v>21.503</v>
       </c>
     </row>
-    <row r="141" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A141" s="2">
         <v>3641</v>
       </c>
@@ -8967,7 +8970,7 @@
         <v>215.035</v>
       </c>
     </row>
-    <row r="142" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A142" s="2">
         <v>3640</v>
       </c>
@@ -9020,7 +9023,7 @@
         <v>21.503</v>
       </c>
     </row>
-    <row r="143" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A143" s="2">
         <v>3639</v>
       </c>
@@ -9073,7 +9076,7 @@
         <v>21.503</v>
       </c>
     </row>
-    <row r="144" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A144" s="2">
         <v>3637</v>
       </c>
@@ -9126,7 +9129,7 @@
         <v>858.92399999999998</v>
       </c>
     </row>
-    <row r="145" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A145" s="2">
         <v>3635</v>
       </c>
@@ -9179,7 +9182,7 @@
         <v>429.46199999999999</v>
       </c>
     </row>
-    <row r="146" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A146" s="2">
         <v>3634</v>
       </c>
@@ -9232,7 +9235,7 @@
         <v>21.472999999999999</v>
       </c>
     </row>
-    <row r="147" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A147" s="2">
         <v>3633</v>
       </c>
@@ -9285,7 +9288,7 @@
         <v>21.472999999999999</v>
       </c>
     </row>
-    <row r="148" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A148" s="2">
         <v>3632</v>
       </c>
@@ -9338,7 +9341,7 @@
         <v>21.472999999999999</v>
       </c>
     </row>
-    <row r="149" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A149" s="2">
         <v>3630</v>
       </c>
@@ -9391,7 +9394,7 @@
         <v>858.92399999999998</v>
       </c>
     </row>
-    <row r="150" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A150" s="2">
         <v>3627</v>
       </c>
@@ -9444,7 +9447,7 @@
         <v>428.57100000000003</v>
       </c>
     </row>
-    <row r="151" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A151" s="2">
         <v>3626</v>
       </c>
@@ -9497,7 +9500,7 @@
         <v>427.80099999999999</v>
       </c>
     </row>
-    <row r="152" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A152" s="2">
         <v>3622</v>
       </c>
@@ -9544,7 +9547,7 @@
         <v>102.4</v>
       </c>
     </row>
-    <row r="153" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A153" s="2">
         <v>3620</v>
       </c>
@@ -9591,7 +9594,7 @@
         <v>102.4</v>
       </c>
     </row>
-    <row r="154" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A154" s="2">
         <v>3617</v>
       </c>
@@ -9644,7 +9647,7 @@
         <v>86.241</v>
       </c>
     </row>
-    <row r="155" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A155" s="2">
         <v>3618</v>
       </c>
@@ -9691,7 +9694,7 @@
         <v>102.4</v>
       </c>
     </row>
-    <row r="156" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A156" s="2">
         <v>3616</v>
       </c>
@@ -9738,7 +9741,7 @@
         <v>102.4</v>
       </c>
     </row>
-    <row r="157" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A157" s="2">
         <v>3613</v>
       </c>
@@ -9791,7 +9794,7 @@
         <v>2584.306</v>
       </c>
     </row>
-    <row r="158" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A158" s="2">
         <v>3612</v>
       </c>
@@ -9838,7 +9841,7 @@
         <v>102.4</v>
       </c>
     </row>
-    <row r="159" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A159" s="2">
         <v>3610</v>
       </c>
@@ -9885,7 +9888,7 @@
         <v>102.4</v>
       </c>
     </row>
-    <row r="160" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A160" s="2">
         <v>3608</v>
       </c>
@@ -9938,7 +9941,7 @@
         <v>86.33</v>
       </c>
     </row>
-    <row r="161" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A161" s="2">
         <v>3606</v>
       </c>
@@ -9991,7 +9994,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="162" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A162" s="2">
         <v>3604</v>
       </c>
@@ -10044,7 +10047,7 @@
         <v>122.88</v>
       </c>
     </row>
-    <row r="163" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A163" s="2">
         <v>3603</v>
       </c>
@@ -10097,7 +10100,7 @@
         <v>5.12</v>
       </c>
     </row>
-    <row r="164" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A164" s="2">
         <v>3600</v>
       </c>
@@ -10144,7 +10147,7 @@
         <v>434.68599999999998</v>
       </c>
     </row>
-    <row r="165" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A165" s="2">
         <v>3599</v>
       </c>
@@ -10191,7 +10194,7 @@
         <v>434.68599999999998</v>
       </c>
     </row>
-    <row r="166" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A166" s="2">
         <v>3597</v>
       </c>
@@ -10244,7 +10247,7 @@
         <v>434.68599999999998</v>
       </c>
     </row>
-    <row r="167" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A167" s="2">
         <v>3596</v>
       </c>
@@ -10297,7 +10300,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="168" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A168" s="2">
         <v>3595</v>
       </c>
@@ -10350,7 +10353,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="169" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A169" s="2">
         <v>3593</v>
       </c>
@@ -10403,7 +10406,7 @@
         <v>5.12</v>
       </c>
     </row>
-    <row r="170" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A170" s="2">
         <v>3590</v>
       </c>
@@ -10456,7 +10459,7 @@
         <v>21.693999999999999</v>
       </c>
     </row>
-    <row r="171" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A171" s="2">
         <v>3588</v>
       </c>
@@ -10509,7 +10512,7 @@
         <v>10.24</v>
       </c>
     </row>
-    <row r="172" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A172" s="2">
         <v>3586</v>
       </c>
@@ -10562,7 +10565,7 @@
         <v>20.48</v>
       </c>
     </row>
-    <row r="173" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A173" s="2">
         <v>3584</v>
       </c>
@@ -10615,7 +10618,7 @@
         <v>21.693999999999999</v>
       </c>
     </row>
-    <row r="174" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A174" s="2">
         <v>3577</v>
       </c>
@@ -10668,7 +10671,7 @@
         <v>86.775000000000006</v>
       </c>
     </row>
-    <row r="175" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A175" s="2">
         <v>3575</v>
       </c>
@@ -10721,7 +10724,7 @@
         <v>102.4</v>
       </c>
     </row>
-    <row r="176" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A176" s="2">
         <v>3572</v>
       </c>
@@ -10774,7 +10777,7 @@
         <v>5.12</v>
       </c>
     </row>
-    <row r="177" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A177" s="2">
         <v>3571</v>
       </c>
@@ -10827,7 +10830,7 @@
         <v>5.12</v>
       </c>
     </row>
-    <row r="178" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A178" s="2">
         <v>3570</v>
       </c>
@@ -10880,7 +10883,7 @@
         <v>56.32</v>
       </c>
     </row>
-    <row r="179" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A179" s="2">
         <v>3568</v>
       </c>
@@ -10933,7 +10936,7 @@
         <v>43.432000000000002</v>
       </c>
     </row>
-    <row r="180" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A180" s="2">
         <v>3567</v>
       </c>
@@ -10986,7 +10989,7 @@
         <v>43.432000000000002</v>
       </c>
     </row>
-    <row r="181" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A181" s="2">
         <v>3566</v>
       </c>
@@ -11039,7 +11042,7 @@
         <v>173.72900000000001</v>
       </c>
     </row>
-    <row r="182" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A182" s="2">
         <v>3564</v>
       </c>
@@ -11092,7 +11095,7 @@
         <v>173.72900000000001</v>
       </c>
     </row>
-    <row r="183" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A183" s="2">
         <v>3560</v>
       </c>
@@ -11145,7 +11148,7 @@
         <v>433.512</v>
       </c>
     </row>
-    <row r="184" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A184" s="2">
         <v>3558</v>
       </c>
@@ -11198,7 +11201,7 @@
         <v>433.512</v>
       </c>
     </row>
-    <row r="185" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A185" s="2">
         <v>3554</v>
       </c>
@@ -11251,7 +11254,7 @@
         <v>187.85499999999999</v>
       </c>
     </row>
-    <row r="186" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A186" s="2">
         <v>3549</v>
       </c>
@@ -11298,7 +11301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A187" s="2">
         <v>3548</v>
       </c>
@@ -11345,7 +11348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A188" s="2">
         <v>3547</v>
       </c>
@@ -11392,7 +11395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A189" s="2">
         <v>3545</v>
       </c>
@@ -11445,7 +11448,7 @@
         <v>10.24</v>
       </c>
     </row>
-    <row r="190" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A190" s="2">
         <v>3543</v>
       </c>
@@ -11498,7 +11501,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="191" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A191" s="2">
         <v>3541</v>
       </c>
@@ -11551,7 +11554,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="192" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A192" s="2">
         <v>3539</v>
       </c>
@@ -11604,7 +11607,7 @@
         <v>138.24</v>
       </c>
     </row>
-    <row r="193" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A193" s="2">
         <v>3538</v>
       </c>
@@ -11657,7 +11660,7 @@
         <v>20.48</v>
       </c>
     </row>
-    <row r="194" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A194" s="2">
         <v>3537</v>
       </c>
@@ -11710,7 +11713,7 @@
         <v>138.24</v>
       </c>
     </row>
-    <row r="195" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A195" s="2">
         <v>3536</v>
       </c>
@@ -11763,7 +11766,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="196" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A196" s="2">
         <v>3532</v>
       </c>
@@ -11816,7 +11819,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="197" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A197" s="2">
         <v>3531</v>
       </c>
@@ -11869,7 +11872,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="198" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A198" s="2">
         <v>3529</v>
       </c>
@@ -11922,7 +11925,7 @@
         <v>469.63799999999998</v>
       </c>
     </row>
-    <row r="199" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A199" s="2">
         <v>3524</v>
       </c>
@@ -11975,7 +11978,7 @@
         <v>20.48</v>
       </c>
     </row>
-    <row r="200" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A200" s="2">
         <v>3523</v>
       </c>
@@ -12028,7 +12031,7 @@
         <v>40.96</v>
       </c>
     </row>
-    <row r="201" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A201" s="2">
         <v>3517</v>
       </c>
@@ -12081,7 +12084,7 @@
         <v>250.88</v>
       </c>
     </row>
-    <row r="202" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A202" s="2">
         <v>3516</v>
       </c>
@@ -12134,7 +12137,7 @@
         <v>250.88</v>
       </c>
     </row>
-    <row r="203" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A203" s="2">
         <v>3514</v>
       </c>
@@ -12187,7 +12190,7 @@
         <v>30.72</v>
       </c>
     </row>
-    <row r="204" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A204" s="2">
         <v>3513</v>
       </c>
@@ -12240,7 +12243,7 @@
         <v>430.08</v>
       </c>
     </row>
-    <row r="205" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A205" s="2">
         <v>3512</v>
       </c>
@@ -12293,7 +12296,7 @@
         <v>430.08</v>
       </c>
     </row>
-    <row r="206" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A206" s="2">
         <v>3510</v>
       </c>
@@ -12346,7 +12349,7 @@
         <v>175.09</v>
       </c>
     </row>
-    <row r="207" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A207" s="2">
         <v>3508</v>
       </c>
@@ -12399,7 +12402,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="208" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A208" s="2">
         <v>3506</v>
       </c>
@@ -12452,7 +12455,7 @@
         <v>2634.1210000000001</v>
       </c>
     </row>
-    <row r="209" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A209" s="2">
         <v>3601</v>
       </c>
@@ -12505,7 +12508,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="210" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A210" s="2">
         <v>3504</v>
       </c>
@@ -12558,7 +12561,7 @@
         <v>230.4</v>
       </c>
     </row>
-    <row r="211" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A211" s="2">
         <v>3502</v>
       </c>
@@ -12611,7 +12614,7 @@
         <v>1008.64</v>
       </c>
     </row>
-    <row r="212" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A212" s="2">
         <v>3499</v>
       </c>
@@ -12664,7 +12667,7 @@
         <v>44.091999999999999</v>
       </c>
     </row>
-    <row r="213" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A213" s="2">
         <v>3497</v>
       </c>
@@ -12717,7 +12720,7 @@
         <v>440.923</v>
       </c>
     </row>
-    <row r="214" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A214" s="2">
         <v>3495</v>
       </c>
@@ -12770,7 +12773,7 @@
         <v>440.923</v>
       </c>
     </row>
-    <row r="215" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A215" s="2">
         <v>3493</v>
       </c>
@@ -12823,7 +12826,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="216" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A216" s="2">
         <v>3491</v>
       </c>
@@ -12876,7 +12879,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="217" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A217" s="2">
         <v>3489</v>
       </c>
@@ -12929,7 +12932,7 @@
         <v>5.12</v>
       </c>
     </row>
-    <row r="218" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A218" s="2">
         <v>3484</v>
       </c>
@@ -12982,7 +12985,7 @@
         <v>1325.3219999999999</v>
       </c>
     </row>
-    <row r="219" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A219" s="2">
         <v>3481</v>
       </c>
@@ -13035,7 +13038,7 @@
         <v>2295.54</v>
       </c>
     </row>
-    <row r="220" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A220" s="2">
         <v>3480</v>
       </c>
@@ -13088,7 +13091,7 @@
         <v>35.316000000000003</v>
       </c>
     </row>
-    <row r="221" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A221" s="2">
         <v>3479</v>
       </c>
@@ -13141,7 +13144,7 @@
         <v>22.073</v>
       </c>
     </row>
-    <row r="222" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A222" s="2">
         <v>3477</v>
       </c>
@@ -13194,7 +13197,7 @@
         <v>52.973999999999997</v>
       </c>
     </row>
-    <row r="223" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A223" s="2">
         <v>3476</v>
       </c>
@@ -13241,7 +13244,7 @@
         <v>442.09800000000001</v>
       </c>
     </row>
-    <row r="224" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A224" s="2">
         <v>3474</v>
       </c>
@@ -13288,7 +13291,7 @@
         <v>442.09800000000001</v>
       </c>
     </row>
-    <row r="225" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A225" s="2">
         <v>3473</v>
       </c>
@@ -13341,7 +13344,7 @@
         <v>1105.2460000000001</v>
       </c>
     </row>
-    <row r="226" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A226" s="2">
         <v>3470</v>
       </c>
@@ -13394,7 +13397,7 @@
         <v>1061.0360000000001</v>
       </c>
     </row>
-    <row r="227" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A227" s="2">
         <v>3469</v>
       </c>
@@ -13447,7 +13450,7 @@
         <v>442.09800000000001</v>
       </c>
     </row>
-    <row r="228" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A228" s="2">
         <v>3467</v>
       </c>
@@ -13500,7 +13503,7 @@
         <v>1105.2460000000001</v>
       </c>
     </row>
-    <row r="229" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A229" s="2">
         <v>3465</v>
       </c>
@@ -13553,7 +13556,7 @@
         <v>176.839</v>
       </c>
     </row>
-    <row r="230" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A230" s="2">
         <v>3459</v>
       </c>
@@ -13606,7 +13609,7 @@
         <v>22.125</v>
       </c>
     </row>
-    <row r="231" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A231" s="2">
         <v>3457</v>
       </c>
@@ -13659,7 +13662,7 @@
         <v>2655.018</v>
       </c>
     </row>
-    <row r="232" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A232" s="2">
         <v>3456</v>
       </c>
@@ -13712,7 +13715,7 @@
         <v>606.22900000000004</v>
       </c>
     </row>
-    <row r="233" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A233" s="2">
         <v>3455</v>
       </c>
@@ -13765,7 +13768,7 @@
         <v>22.125</v>
       </c>
     </row>
-    <row r="234" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A234" s="2">
         <v>3454</v>
       </c>
@@ -13818,7 +13821,7 @@
         <v>22.125</v>
       </c>
     </row>
-    <row r="235" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A235" s="2">
         <v>3451</v>
       </c>
@@ -13871,7 +13874,7 @@
         <v>265.50200000000001</v>
       </c>
     </row>
-    <row r="236" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A236" s="2">
         <v>3449</v>
       </c>
@@ -13924,7 +13927,7 @@
         <v>88.501000000000005</v>
       </c>
     </row>
-    <row r="237" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A237" s="2">
         <v>3448</v>
       </c>
@@ -13977,7 +13980,7 @@
         <v>44.267000000000003</v>
       </c>
     </row>
-    <row r="238" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A238" s="2">
         <v>3445</v>
       </c>
@@ -14030,7 +14033,7 @@
         <v>265.59899999999999</v>
       </c>
     </row>
-    <row r="239" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A239" s="2">
         <v>3443</v>
       </c>
@@ -14083,7 +14086,7 @@
         <v>88.533000000000001</v>
       </c>
     </row>
-    <row r="240" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A240" s="2">
         <v>3441</v>
       </c>
@@ -14136,7 +14139,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="241" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A241" s="2">
         <v>3439</v>
       </c>
@@ -14189,7 +14192,7 @@
         <v>2655.99</v>
       </c>
     </row>
-    <row r="242" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A242" s="2">
         <v>3436</v>
       </c>
@@ -14242,7 +14245,7 @@
         <v>15.36</v>
       </c>
     </row>
-    <row r="243" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A243" s="2">
         <v>3435</v>
       </c>
@@ -14295,7 +14298,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="244" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A244" s="2">
         <v>3433</v>
       </c>
@@ -14348,7 +14351,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="245" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A245" s="2">
         <v>3415</v>
       </c>
@@ -14401,7 +14404,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="246" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A246" s="2">
         <v>3413</v>
       </c>
@@ -14454,7 +14457,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="247" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A247" s="2">
         <v>3411</v>
       </c>
@@ -14507,7 +14510,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="248" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A248" s="2">
         <v>3408</v>
       </c>
@@ -14560,7 +14563,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="249" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A249" s="2">
         <v>3407</v>
       </c>
@@ -14613,7 +14616,7 @@
         <v>122.88</v>
       </c>
     </row>
-    <row r="250" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A250" s="2">
         <v>3405</v>
       </c>
@@ -14666,7 +14669,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="251" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A251" s="2">
         <v>3403</v>
       </c>
@@ -14719,7 +14722,7 @@
         <v>88.549000000000007</v>
       </c>
     </row>
-    <row r="252" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A252" s="2">
         <v>3401</v>
       </c>
@@ -14772,7 +14775,7 @@
         <v>265.64800000000002</v>
       </c>
     </row>
-    <row r="253" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A253" s="2">
         <v>3399</v>
       </c>
@@ -14825,7 +14828,7 @@
         <v>88.549000000000007</v>
       </c>
     </row>
-    <row r="254" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A254" s="2">
         <v>3397</v>
       </c>
@@ -14878,7 +14881,7 @@
         <v>88.549000000000007</v>
       </c>
     </row>
-    <row r="255" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A255" s="2">
         <v>3395</v>
       </c>
@@ -14931,7 +14934,7 @@
         <v>88.978999999999999</v>
       </c>
     </row>
-    <row r="256" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A256" s="2">
         <v>3393</v>
       </c>
@@ -14984,7 +14987,7 @@
         <v>89.286000000000001</v>
       </c>
     </row>
-    <row r="257" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A257" s="2">
         <v>3389</v>
       </c>
@@ -15037,7 +15040,7 @@
         <v>178.57300000000001</v>
       </c>
     </row>
-    <row r="258" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A258" s="2">
         <v>3388</v>
       </c>
@@ -15090,7 +15093,7 @@
         <v>178.36199999999999</v>
       </c>
     </row>
-    <row r="259" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A259" s="2">
         <v>3386</v>
       </c>
@@ -15143,7 +15146,7 @@
         <v>44.591000000000001</v>
       </c>
     </row>
-    <row r="260" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A260" s="2">
         <v>3384</v>
       </c>
@@ -15196,7 +15199,7 @@
         <v>45.055999999999997</v>
       </c>
     </row>
-    <row r="261" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A261" s="2">
         <v>3382</v>
       </c>
@@ -15249,7 +15252,7 @@
         <v>2703.3760000000002</v>
       </c>
     </row>
-    <row r="262" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A262" s="2">
         <v>3379</v>
       </c>
@@ -15302,7 +15305,7 @@
         <v>44.789000000000001</v>
       </c>
     </row>
-    <row r="263" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A263" s="2">
         <v>3378</v>
       </c>
@@ -15355,7 +15358,7 @@
         <v>447.88900000000001</v>
       </c>
     </row>
-    <row r="264" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A264" s="2">
         <v>3376</v>
       </c>
@@ -15408,7 +15411,7 @@
         <v>447.88900000000001</v>
       </c>
     </row>
-    <row r="265" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A265" s="2">
         <v>3374</v>
       </c>
@@ -15461,7 +15464,7 @@
         <v>2687.337</v>
       </c>
     </row>
-    <row r="266" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A266" s="2">
         <v>3372</v>
       </c>
@@ -15514,7 +15517,7 @@
         <v>1348.164</v>
       </c>
     </row>
-    <row r="267" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A267" s="2">
         <v>3364</v>
       </c>
@@ -15567,7 +15570,7 @@
         <v>77.090999999999994</v>
       </c>
     </row>
-    <row r="268" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A268" s="2">
         <v>3362</v>
       </c>
@@ -15620,7 +15623,7 @@
         <v>2720.8719999999998</v>
       </c>
     </row>
-    <row r="269" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A269" s="2">
         <v>3361</v>
       </c>
@@ -15673,7 +15676,7 @@
         <v>376.387</v>
       </c>
     </row>
-    <row r="270" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A270" s="2">
         <v>3356</v>
       </c>
@@ -15726,7 +15729,7 @@
         <v>2734.9650000000001</v>
       </c>
     </row>
-    <row r="271" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A271" s="2">
         <v>3354</v>
       </c>
@@ -15779,7 +15782,7 @@
         <v>1093.9860000000001</v>
       </c>
     </row>
-    <row r="272" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A272" s="2">
         <v>3351</v>
       </c>
@@ -15832,7 +15835,7 @@
         <v>908.90099999999995</v>
       </c>
     </row>
-    <row r="273" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A273" s="2">
         <v>3350</v>
       </c>
@@ -15885,7 +15888,7 @@
         <v>1363.3520000000001</v>
       </c>
     </row>
-    <row r="274" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A274" s="2">
         <v>3347</v>
       </c>
@@ -15938,7 +15941,7 @@
         <v>61.052999999999997</v>
       </c>
     </row>
-    <row r="275" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A275" s="2">
         <v>3346</v>
       </c>
@@ -15991,7 +15994,7 @@
         <v>704.45699999999999</v>
       </c>
     </row>
-    <row r="276" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A276" s="2">
         <v>3342</v>
       </c>
@@ -16044,7 +16047,7 @@
         <v>44.639000000000003</v>
       </c>
     </row>
-    <row r="277" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A277" s="2">
         <v>3340</v>
       </c>
@@ -16097,7 +16100,7 @@
         <v>446.39100000000002</v>
       </c>
     </row>
-    <row r="278" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A278" s="2">
         <v>3339</v>
       </c>
@@ -16150,7 +16153,7 @@
         <v>446.39100000000002</v>
       </c>
     </row>
-    <row r="279" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A279" s="2">
         <v>3338</v>
       </c>
@@ -16203,7 +16206,7 @@
         <v>446.39100000000002</v>
       </c>
     </row>
-    <row r="280" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A280" s="2">
         <v>3335</v>
       </c>
@@ -16256,7 +16259,7 @@
         <v>443.71800000000002</v>
       </c>
     </row>
-    <row r="281" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A281" s="2">
         <v>3329</v>
       </c>
@@ -16309,7 +16312,7 @@
         <v>443.71800000000002</v>
       </c>
     </row>
-    <row r="282" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A282" s="2">
         <v>3328</v>
       </c>
@@ -16362,7 +16365,7 @@
         <v>887.43600000000004</v>
       </c>
     </row>
-    <row r="283" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A283" s="2">
         <v>3370</v>
       </c>
@@ -16415,7 +16418,7 @@
         <v>264.57799999999997</v>
       </c>
     </row>
-    <row r="284" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A284" s="2">
         <v>3319</v>
       </c>
@@ -16468,7 +16471,7 @@
         <v>35.840000000000003</v>
       </c>
     </row>
-    <row r="285" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A285" s="2">
         <v>3318</v>
       </c>
@@ -16521,7 +16524,7 @@
         <v>54.42</v>
       </c>
     </row>
-    <row r="286" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A286" s="2">
         <v>3317</v>
       </c>
@@ -16574,7 +16577,7 @@
         <v>176.386</v>
       </c>
     </row>
-    <row r="287" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A287" s="2">
         <v>3311</v>
       </c>
@@ -16627,7 +16630,7 @@
         <v>44.095999999999997</v>
       </c>
     </row>
-    <row r="288" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A288" s="2">
         <v>3310</v>
       </c>
@@ -16680,7 +16683,7 @@
         <v>44.140999999999998</v>
       </c>
     </row>
-    <row r="289" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A289" s="2">
         <v>3306</v>
       </c>
@@ -16733,7 +16736,7 @@
         <v>44.140999999999998</v>
       </c>
     </row>
-    <row r="290" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A290" s="2">
         <v>3305</v>
       </c>
@@ -16786,7 +16789,7 @@
         <v>44.06</v>
       </c>
     </row>
-    <row r="291" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A291" s="2">
         <v>3304</v>
       </c>
@@ -16839,7 +16842,7 @@
         <v>88.25</v>
       </c>
     </row>
-    <row r="292" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A292" s="2">
         <v>3303</v>
       </c>
@@ -16892,7 +16895,7 @@
         <v>220.70500000000001</v>
       </c>
     </row>
-    <row r="293" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A293" s="2">
         <v>3302</v>
       </c>
@@ -16945,7 +16948,7 @@
         <v>44.140999999999998</v>
       </c>
     </row>
-    <row r="294" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A294" s="2">
         <v>3301</v>
       </c>
@@ -16998,7 +17001,7 @@
         <v>176.56399999999999</v>
       </c>
     </row>
-    <row r="295" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A295" s="2">
         <v>3300</v>
       </c>
@@ -17051,7 +17054,7 @@
         <v>220.70500000000001</v>
       </c>
     </row>
-    <row r="296" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A296" s="2">
         <v>3299</v>
       </c>
@@ -17104,7 +17107,7 @@
         <v>88.281999999999996</v>
       </c>
     </row>
-    <row r="297" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A297" s="2">
         <v>3298</v>
       </c>
@@ -17157,7 +17160,7 @@
         <v>35.840000000000003</v>
       </c>
     </row>
-    <row r="298" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A298" s="2">
         <v>3297</v>
       </c>
@@ -17210,7 +17213,7 @@
         <v>56.32</v>
       </c>
     </row>
-    <row r="299" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A299" s="2">
         <v>3296</v>
       </c>
@@ -17263,7 +17266,7 @@
         <v>35.840000000000003</v>
       </c>
     </row>
-    <row r="300" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A300" s="2">
         <v>3295</v>
       </c>
@@ -17316,7 +17319,7 @@
         <v>56.32</v>
       </c>
     </row>
-    <row r="301" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A301" s="2">
         <v>3293</v>
       </c>
@@ -17369,7 +17372,7 @@
         <v>88.597999999999999</v>
       </c>
     </row>
-    <row r="302" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A302" s="2">
         <v>3291</v>
       </c>
@@ -17422,7 +17425,7 @@
         <v>56.32</v>
       </c>
     </row>
-    <row r="303" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A303" s="2">
         <v>3289</v>
       </c>
@@ -17475,7 +17478,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="304" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A304" s="2">
         <v>3287</v>
       </c>
@@ -17528,7 +17531,7 @@
         <v>35.840000000000003</v>
       </c>
     </row>
-    <row r="305" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A305" s="2">
         <v>3286</v>
       </c>
@@ -17581,7 +17584,7 @@
         <v>35.840000000000003</v>
       </c>
     </row>
-    <row r="306" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A306" s="2">
         <v>3284</v>
       </c>
@@ -17634,7 +17637,7 @@
         <v>15.36</v>
       </c>
     </row>
-    <row r="307" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A307" s="2">
         <v>3283</v>
       </c>
@@ -17687,7 +17690,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="308" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A308" s="2">
         <v>3282</v>
       </c>
@@ -17740,7 +17743,7 @@
         <v>20.48</v>
       </c>
     </row>
-    <row r="309" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A309" s="2">
         <v>3280</v>
       </c>
@@ -17793,7 +17796,7 @@
         <v>61.44</v>
       </c>
     </row>
-    <row r="310" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A310" s="2">
         <v>3278</v>
       </c>
@@ -17846,7 +17849,7 @@
         <v>5.12</v>
       </c>
     </row>
-    <row r="311" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A311" s="2">
         <v>3276</v>
       </c>
@@ -17899,7 +17902,7 @@
         <v>87.04</v>
       </c>
     </row>
-    <row r="312" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A312" s="2">
         <v>3275</v>
       </c>
@@ -17952,7 +17955,7 @@
         <v>35.840000000000003</v>
       </c>
     </row>
-    <row r="313" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A313" s="2">
         <v>3274</v>
       </c>
@@ -18005,7 +18008,7 @@
         <v>5.12</v>
       </c>
     </row>
-    <row r="314" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A314" s="2">
         <v>3273</v>
       </c>
@@ -18058,7 +18061,7 @@
         <v>266.10899999999998</v>
       </c>
     </row>
-    <row r="315" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A315" s="2">
         <v>3271</v>
       </c>
@@ -18111,7 +18114,7 @@
         <v>15.36</v>
       </c>
     </row>
-    <row r="316" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A316" s="2">
         <v>3269</v>
       </c>
@@ -18164,7 +18167,7 @@
         <v>76.8</v>
       </c>
     </row>
-    <row r="317" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A317" s="2">
         <v>3267</v>
       </c>
@@ -18217,7 +18220,7 @@
         <v>35.840000000000003</v>
       </c>
     </row>
-    <row r="318" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A318" s="2">
         <v>3265</v>
       </c>
@@ -18270,7 +18273,7 @@
         <v>56.32</v>
       </c>
     </row>
-    <row r="319" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A319" s="2">
         <v>3263</v>
       </c>
@@ -18323,7 +18326,7 @@
         <v>20.48</v>
       </c>
     </row>
-    <row r="320" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A320" s="2">
         <v>3256</v>
       </c>
@@ -18376,7 +18379,7 @@
         <v>20.48</v>
       </c>
     </row>
-    <row r="321" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A321" s="2">
         <v>3255</v>
       </c>
@@ -18429,7 +18432,7 @@
         <v>30.72</v>
       </c>
     </row>
-    <row r="322" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A322" s="2">
         <v>3254</v>
       </c>
@@ -18482,7 +18485,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="323" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A323" s="2">
         <v>3252</v>
       </c>
@@ -18535,7 +18538,7 @@
         <v>337.92</v>
       </c>
     </row>
-    <row r="324" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A324" s="2">
         <v>3250</v>
       </c>
@@ -18588,7 +18591,7 @@
         <v>803.84</v>
       </c>
     </row>
-    <row r="325" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A325" s="2">
         <v>3247</v>
       </c>
@@ -18641,7 +18644,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="326" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A326" s="2">
         <v>3246</v>
       </c>
@@ -18694,7 +18697,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="327" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A327" s="2">
         <v>3243</v>
       </c>
@@ -18747,7 +18750,7 @@
         <v>5.12</v>
       </c>
     </row>
-    <row r="328" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A328" s="2">
         <v>3242</v>
       </c>
@@ -18800,7 +18803,7 @@
         <v>46.08</v>
       </c>
     </row>
-    <row r="329" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A329" s="2">
         <v>3241</v>
       </c>
@@ -18853,7 +18856,7 @@
         <v>61.44</v>
       </c>
     </row>
-    <row r="330" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A330" s="2">
         <v>3235</v>
       </c>
@@ -18906,7 +18909,7 @@
         <v>15.36</v>
       </c>
     </row>
-    <row r="331" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A331" s="2">
         <v>3234</v>
       </c>
@@ -18959,7 +18962,7 @@
         <v>20.48</v>
       </c>
     </row>
-    <row r="332" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A332" s="2">
         <v>3233</v>
       </c>
@@ -19012,7 +19015,7 @@
         <v>5.12</v>
       </c>
     </row>
-    <row r="333" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A333" s="2">
         <v>3231</v>
       </c>
@@ -19065,7 +19068,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="334" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A334" s="2">
         <v>3228</v>
       </c>
@@ -19118,7 +19121,7 @@
         <v>76.8</v>
       </c>
     </row>
-    <row r="335" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A335" s="2">
         <v>3227</v>
       </c>
@@ -19171,7 +19174,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="336" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A336" s="2">
         <v>3226</v>
       </c>
@@ -19218,7 +19221,7 @@
         <v>20.48</v>
       </c>
     </row>
-    <row r="337" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A337" s="2">
         <v>3225</v>
       </c>
@@ -19271,7 +19274,7 @@
         <v>81.92</v>
       </c>
     </row>
-    <row r="338" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A338" s="2">
         <v>3218</v>
       </c>
@@ -19324,7 +19327,7 @@
         <v>92.16</v>
       </c>
     </row>
-    <row r="339" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A339" s="2">
         <v>3216</v>
       </c>
@@ -19377,7 +19380,7 @@
         <v>294.02</v>
       </c>
     </row>
-    <row r="340" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A340" s="2">
         <v>3214</v>
       </c>
@@ -19430,7 +19433,7 @@
         <v>35.840000000000003</v>
       </c>
     </row>
-    <row r="341" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A341" s="2">
         <v>3212</v>
       </c>
@@ -19483,7 +19486,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="342" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A342" s="2">
         <v>3211</v>
       </c>
@@ -19536,7 +19539,7 @@
         <v>4.327</v>
       </c>
     </row>
-    <row r="343" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A343" s="2">
         <v>3207</v>
       </c>
@@ -19583,7 +19586,7 @@
         <v>20.48</v>
       </c>
     </row>
-    <row r="344" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A344" s="2">
         <v>3206</v>
       </c>
@@ -19636,7 +19639,7 @@
         <v>38.94</v>
       </c>
     </row>
-    <row r="345" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A345" s="2">
         <v>3205</v>
       </c>
@@ -19689,7 +19692,7 @@
         <v>173.065</v>
       </c>
     </row>
-    <row r="346" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A346" s="2">
         <v>3200</v>
       </c>
@@ -19742,7 +19745,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="347" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A347" s="2">
         <v>3198</v>
       </c>
@@ -19795,7 +19798,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="348" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A348" s="2">
         <v>3196</v>
       </c>
@@ -19848,7 +19851,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="349" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A349" s="2">
         <v>3194</v>
       </c>
@@ -19901,7 +19904,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="350" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A350" s="2">
         <v>3193</v>
       </c>
@@ -19954,7 +19957,7 @@
         <v>10.24</v>
       </c>
     </row>
-    <row r="351" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A351" s="2">
         <v>3191</v>
       </c>
@@ -20007,7 +20010,7 @@
         <v>21.84</v>
       </c>
     </row>
-    <row r="352" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A352" s="2">
         <v>3189</v>
       </c>
@@ -20060,7 +20063,7 @@
         <v>10.24</v>
       </c>
     </row>
-    <row r="353" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A353" s="2">
         <v>3188</v>
       </c>
@@ -20113,7 +20116,7 @@
         <v>21.84</v>
       </c>
     </row>
-    <row r="354" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A354" s="2">
         <v>3186</v>
       </c>
@@ -20166,7 +20169,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="355" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A355" s="2">
         <v>3184</v>
       </c>
@@ -20219,7 +20222,7 @@
         <v>10.24</v>
       </c>
     </row>
-    <row r="356" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A356" s="2">
         <v>3182</v>
       </c>
@@ -20272,7 +20275,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="357" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A357" s="2">
         <v>3180</v>
       </c>
@@ -20325,7 +20328,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="358" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A358" s="2">
         <v>3179</v>
       </c>
@@ -20378,7 +20381,7 @@
         <v>131.572</v>
       </c>
     </row>
-    <row r="359" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A359" s="2">
         <v>3175</v>
       </c>
@@ -20431,7 +20434,7 @@
         <v>44.067999999999998</v>
       </c>
     </row>
-    <row r="360" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A360" s="2">
         <v>3173</v>
       </c>
@@ -20484,7 +20487,7 @@
         <v>35.840000000000003</v>
       </c>
     </row>
-    <row r="361" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A361" s="2">
         <v>3159</v>
       </c>
@@ -20537,7 +20540,7 @@
         <v>1327.9949999999999</v>
       </c>
     </row>
-    <row r="362" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A362" s="2">
         <v>3158</v>
       </c>
@@ -20590,7 +20593,7 @@
         <v>885.33</v>
       </c>
     </row>
-    <row r="363" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A363" s="2">
         <v>3157</v>
       </c>
@@ -20637,7 +20640,7 @@
         <v>629.76</v>
       </c>
     </row>
-    <row r="364" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A364" s="2">
         <v>3156</v>
       </c>
@@ -20684,7 +20687,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="365" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A365" s="2">
         <v>3155</v>
       </c>
@@ -20731,7 +20734,7 @@
         <v>204.8</v>
       </c>
     </row>
-    <row r="366" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A366" s="2">
         <v>3154</v>
       </c>
@@ -20778,7 +20781,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="367" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A367" s="2">
         <v>3152</v>
       </c>
@@ -20831,7 +20834,7 @@
         <v>2213.3249999999998</v>
       </c>
     </row>
-    <row r="368" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A368" s="2">
         <v>3149</v>
       </c>
@@ -20878,7 +20881,7 @@
         <v>204.8</v>
       </c>
     </row>
-    <row r="369" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A369" s="2">
         <v>3148</v>
       </c>
@@ -20925,7 +20928,7 @@
         <v>629.76</v>
       </c>
     </row>
-    <row r="370" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A370" s="2">
         <v>3147</v>
       </c>
@@ -20972,7 +20975,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="371" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A371" s="2">
         <v>3145</v>
       </c>
@@ -21025,7 +21028,7 @@
         <v>79.680000000000007</v>
       </c>
     </row>
-    <row r="372" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A372" s="2">
         <v>3142</v>
       </c>
@@ -21078,7 +21081,7 @@
         <v>177.066</v>
       </c>
     </row>
-    <row r="373" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A373" s="2">
         <v>3140</v>
       </c>
@@ -21131,7 +21134,7 @@
         <v>544.47799999999995</v>
       </c>
     </row>
-    <row r="374" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A374" s="2">
         <v>3139</v>
       </c>
@@ -21184,7 +21187,7 @@
         <v>442.66500000000002</v>
       </c>
     </row>
-    <row r="375" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A375" s="2">
         <v>3137</v>
       </c>
@@ -21237,7 +21240,7 @@
         <v>665.21299999999997</v>
       </c>
     </row>
-    <row r="376" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A376" s="2">
         <v>3134</v>
       </c>
@@ -21290,7 +21293,7 @@
         <v>630.25199999999995</v>
       </c>
     </row>
-    <row r="377" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A377" s="2">
         <v>3131</v>
       </c>
@@ -21343,7 +21346,7 @@
         <v>221.92</v>
       </c>
     </row>
-    <row r="378" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A378" s="2">
         <v>3130</v>
       </c>
@@ -21396,7 +21399,7 @@
         <v>2219.1979999999999</v>
       </c>
     </row>
-    <row r="379" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A379" s="2">
         <v>3128</v>
       </c>
@@ -21449,7 +21452,7 @@
         <v>88.768000000000001</v>
       </c>
     </row>
-    <row r="380" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A380" s="2">
         <v>3126</v>
       </c>
@@ -21502,7 +21505,7 @@
         <v>310.68799999999999</v>
       </c>
     </row>
-    <row r="381" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A381" s="2">
         <v>3123</v>
       </c>
@@ -21555,7 +21558,7 @@
         <v>310.68799999999999</v>
       </c>
     </row>
-    <row r="382" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A382" s="2">
         <v>3121</v>
       </c>
@@ -21608,7 +21611,7 @@
         <v>124.27500000000001</v>
       </c>
     </row>
-    <row r="383" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A383" s="2">
         <v>3119</v>
       </c>
@@ -21661,7 +21664,7 @@
         <v>887.67899999999997</v>
       </c>
     </row>
-    <row r="384" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A384" s="2">
         <v>3118</v>
       </c>
@@ -21714,7 +21717,7 @@
         <v>887.67899999999997</v>
       </c>
     </row>
-    <row r="385" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A385" s="2">
         <v>3107</v>
       </c>
@@ -21767,7 +21770,7 @@
         <v>179.399</v>
       </c>
     </row>
-    <row r="386" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A386" s="2">
         <v>3105</v>
       </c>
@@ -21820,7 +21823,7 @@
         <v>2236.2080000000001</v>
       </c>
     </row>
-    <row r="387" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A387" s="2">
         <v>3103</v>
       </c>
@@ -21873,7 +21876,7 @@
         <v>2683.4490000000001</v>
       </c>
     </row>
-    <row r="388" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A388" s="2">
         <v>3101</v>
       </c>
@@ -21926,7 +21929,7 @@
         <v>2683.4490000000001</v>
       </c>
     </row>
-    <row r="389" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A389" s="2">
         <v>3100</v>
       </c>
@@ -21979,7 +21982,7 @@
         <v>152.06200000000001</v>
       </c>
     </row>
-    <row r="390" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A390" s="2">
         <v>3099</v>
       </c>
@@ -22032,7 +22035,7 @@
         <v>44.408000000000001</v>
       </c>
     </row>
-    <row r="391" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A391" s="2">
         <v>3098</v>
       </c>
@@ -22085,7 +22088,7 @@
         <v>177.63300000000001</v>
       </c>
     </row>
-    <row r="392" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A392" s="2">
         <v>3097</v>
       </c>
@@ -22138,7 +22141,7 @@
         <v>666.12400000000002</v>
       </c>
     </row>
-    <row r="393" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A393" s="2">
         <v>3096</v>
       </c>
@@ -22191,7 +22194,7 @@
         <v>177.63300000000001</v>
       </c>
     </row>
-    <row r="394" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A394" s="2">
         <v>3095</v>
       </c>
@@ -22244,7 +22247,7 @@
         <v>546.221</v>
       </c>
     </row>
-    <row r="395" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A395" s="2">
         <v>3094</v>
       </c>
@@ -22297,7 +22300,7 @@
         <v>444.08199999999999</v>
       </c>
     </row>
-    <row r="396" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A396" s="2">
         <v>3085</v>
       </c>
@@ -22350,7 +22353,7 @@
         <v>308.58</v>
       </c>
     </row>
-    <row r="397" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A397" s="2">
         <v>3083</v>
       </c>
@@ -22403,7 +22406,7 @@
         <v>729.36</v>
       </c>
     </row>
-    <row r="398" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A398" s="2">
         <v>3077</v>
       </c>
@@ -22456,7 +22459,7 @@
         <v>447.20100000000002</v>
       </c>
     </row>
-    <row r="399" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A399" s="2">
         <v>3076</v>
       </c>
@@ -22509,7 +22512,7 @@
         <v>22.36</v>
       </c>
     </row>
-    <row r="400" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A400" s="2">
         <v>3075</v>
       </c>
@@ -22562,7 +22565,7 @@
         <v>15.36</v>
       </c>
     </row>
-    <row r="401" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A401" s="2">
         <v>3074</v>
       </c>
@@ -22615,7 +22618,7 @@
         <v>357.76100000000002</v>
       </c>
     </row>
-    <row r="402" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A402" s="2">
         <v>3071</v>
       </c>
@@ -22662,7 +22665,7 @@
         <v>44.72</v>
       </c>
     </row>
-    <row r="403" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A403" s="2">
         <v>3070</v>
       </c>
@@ -22715,7 +22718,7 @@
         <v>223.601</v>
       </c>
     </row>
-    <row r="404" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A404" s="2">
         <v>3069</v>
       </c>
@@ -22762,7 +22765,7 @@
         <v>44.72</v>
       </c>
     </row>
-    <row r="405" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A405" s="2">
         <v>3068</v>
       </c>
@@ -22815,7 +22818,7 @@
         <v>134.16</v>
       </c>
     </row>
-    <row r="406" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A406" s="2">
         <v>3067</v>
       </c>
@@ -22862,7 +22865,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="407" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A407" s="2">
         <v>3066</v>
       </c>
@@ -22909,7 +22912,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="408" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A408" s="2">
         <v>3065</v>
       </c>
@@ -22962,7 +22965,7 @@
         <v>98.384</v>
       </c>
     </row>
-    <row r="409" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A409" s="2">
         <v>3064</v>
       </c>
@@ -23015,7 +23018,7 @@
         <v>420.36900000000003</v>
       </c>
     </row>
-    <row r="410" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A410" s="2">
         <v>3063</v>
       </c>
@@ -23068,7 +23071,7 @@
         <v>339.87299999999999</v>
       </c>
     </row>
-    <row r="411" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A411" s="2">
         <v>3061</v>
       </c>
@@ -23121,7 +23124,7 @@
         <v>10.24</v>
       </c>
     </row>
-    <row r="412" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A412" s="2">
         <v>3059</v>
       </c>
@@ -23174,7 +23177,7 @@
         <v>10.24</v>
       </c>
     </row>
-    <row r="413" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A413" s="2">
         <v>3057</v>
       </c>
@@ -23227,7 +23230,7 @@
         <v>46.08</v>
       </c>
     </row>
-    <row r="414" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A414" s="2">
         <v>3055</v>
       </c>
@@ -23280,7 +23283,7 @@
         <v>46.08</v>
       </c>
     </row>
-    <row r="415" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A415" s="2">
         <v>3053</v>
       </c>
@@ -23333,7 +23336,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="416" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A416" s="2">
         <v>3050</v>
       </c>
@@ -23386,7 +23389,7 @@
         <v>10.24</v>
       </c>
     </row>
-    <row r="417" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A417" s="2">
         <v>3049</v>
       </c>
@@ -23439,7 +23442,7 @@
         <v>15.36</v>
       </c>
     </row>
-    <row r="418" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A418" s="2">
         <v>3047</v>
       </c>
@@ -23492,7 +23495,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="419" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A419" s="2">
         <v>3045</v>
       </c>
@@ -23545,7 +23548,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="420" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A420" s="2">
         <v>3044</v>
       </c>
@@ -23598,7 +23601,7 @@
         <v>89.44</v>
       </c>
     </row>
-    <row r="421" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A421" s="2">
         <v>3042</v>
       </c>
@@ -23651,7 +23654,7 @@
         <v>357.76100000000002</v>
       </c>
     </row>
-    <row r="422" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A422" s="2">
         <v>3032</v>
       </c>
@@ -23704,7 +23707,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="423" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A423" s="2">
         <v>3031</v>
       </c>
@@ -23757,7 +23760,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="424" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A424" s="2">
         <v>3030</v>
       </c>
@@ -23810,7 +23813,7 @@
         <v>15.36</v>
       </c>
     </row>
-    <row r="425" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A425" s="2">
         <v>3029</v>
       </c>
@@ -23863,7 +23866,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="426" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A426" s="2">
         <v>3028</v>
       </c>
@@ -23916,7 +23919,7 @@
         <v>15.36</v>
       </c>
     </row>
-    <row r="427" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A427" s="2">
         <v>3027</v>
       </c>
@@ -23969,7 +23972,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="428" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A428" s="2">
         <v>3026</v>
       </c>
@@ -24022,7 +24025,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="429" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A429" s="2">
         <v>3023</v>
       </c>
@@ -24075,7 +24078,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="430" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A430" s="2">
         <v>3022</v>
       </c>
@@ -24128,7 +24131,7 @@
         <v>102.4</v>
       </c>
     </row>
-    <row r="431" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A431" s="2">
         <v>3021</v>
       </c>
@@ -24181,7 +24184,7 @@
         <v>22.353999999999999</v>
       </c>
     </row>
-    <row r="432" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A432" s="2">
         <v>3020</v>
       </c>
@@ -24234,7 +24237,7 @@
         <v>1126.6410000000001</v>
       </c>
     </row>
-    <row r="433" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A433" s="2">
         <v>3019</v>
       </c>
@@ -24287,7 +24290,7 @@
         <v>20.48</v>
       </c>
     </row>
-    <row r="434" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A434" s="2">
         <v>3018</v>
       </c>
@@ -24340,7 +24343,7 @@
         <v>40.96</v>
       </c>
     </row>
-    <row r="435" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A435" s="2">
         <v>3015</v>
       </c>
@@ -24393,7 +24396,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="436" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A436" s="2">
         <v>3014</v>
       </c>
@@ -24446,7 +24449,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="437" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A437" s="2">
         <v>3012</v>
       </c>
@@ -24499,7 +24502,7 @@
         <v>214.268</v>
       </c>
     </row>
-    <row r="438" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A438" s="2">
         <v>3040</v>
       </c>
@@ -24552,7 +24555,7 @@
         <v>668.37099999999998</v>
       </c>
     </row>
-    <row r="439" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A439" s="2">
         <v>3008</v>
       </c>
@@ -24605,7 +24608,7 @@
         <v>668.37099999999998</v>
       </c>
     </row>
-    <row r="440" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A440" s="2">
         <v>3002</v>
       </c>
@@ -24658,7 +24661,7 @@
         <v>1336.742</v>
       </c>
     </row>
-    <row r="441" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A441" s="2">
         <v>3001</v>
       </c>
@@ -24711,7 +24714,7 @@
         <v>1336.742</v>
       </c>
     </row>
-    <row r="442" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A442" s="2">
         <v>3000</v>
       </c>
@@ -24764,7 +24767,7 @@
         <v>89.116</v>
       </c>
     </row>
-    <row r="443" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A443" s="2">
         <v>2998</v>
       </c>
@@ -24817,7 +24820,7 @@
         <v>2673.4850000000001</v>
       </c>
     </row>
-    <row r="444" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A444" s="2">
         <v>2993</v>
       </c>
@@ -24870,7 +24873,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="445" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A445" s="2">
         <v>2992</v>
       </c>
@@ -24923,7 +24926,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="446" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A446" s="2">
         <v>2985</v>
       </c>
@@ -24976,7 +24979,7 @@
         <v>1556.1310000000001</v>
       </c>
     </row>
-    <row r="447" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A447" s="2">
         <v>2982</v>
       </c>
@@ -25029,7 +25032,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="448" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A448" s="2">
         <v>2981</v>
       </c>
@@ -25082,7 +25085,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="449" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A449" s="2">
         <v>2980</v>
       </c>
@@ -25135,7 +25138,7 @@
         <v>88.921999999999997</v>
       </c>
     </row>
-    <row r="450" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A450" s="2">
         <v>2979</v>
       </c>
@@ -25188,7 +25191,7 @@
         <v>222.304</v>
       </c>
     </row>
-    <row r="451" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A451" s="2">
         <v>2978</v>
       </c>
@@ -25241,7 +25244,7 @@
         <v>133.38300000000001</v>
       </c>
     </row>
-    <row r="452" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A452" s="2">
         <v>2977</v>
       </c>
@@ -25294,7 +25297,7 @@
         <v>222.304</v>
       </c>
     </row>
-    <row r="453" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A453" s="2">
         <v>2976</v>
       </c>
@@ -25347,7 +25350,7 @@
         <v>222.304</v>
       </c>
     </row>
-    <row r="454" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A454" s="2">
         <v>2972</v>
       </c>
@@ -25400,7 +25403,7 @@
         <v>44.460999999999999</v>
       </c>
     </row>
-    <row r="455" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A455" s="2">
         <v>2973</v>
       </c>
@@ -25453,7 +25456,7 @@
         <v>88.646000000000001</v>
       </c>
     </row>
-    <row r="456" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A456" s="2">
         <v>2968</v>
       </c>
@@ -25506,7 +25509,7 @@
         <v>443.23200000000003</v>
       </c>
     </row>
-    <row r="457" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A457" s="2">
         <v>2967</v>
       </c>
@@ -25559,7 +25562,7 @@
         <v>88.646000000000001</v>
       </c>
     </row>
-    <row r="458" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A458" s="2">
         <v>2966</v>
       </c>
@@ -25612,7 +25615,7 @@
         <v>88.646000000000001</v>
       </c>
     </row>
-    <row r="459" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A459" s="2">
         <v>2964</v>
       </c>
@@ -25665,7 +25668,7 @@
         <v>1329.6959999999999</v>
       </c>
     </row>
-    <row r="460" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A460" s="2">
         <v>2963</v>
       </c>
@@ -25718,7 +25721,7 @@
         <v>221.61600000000001</v>
       </c>
     </row>
-    <row r="461" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A461" s="2">
         <v>2962</v>
       </c>
@@ -25771,7 +25774,7 @@
         <v>88.646000000000001</v>
       </c>
     </row>
-    <row r="462" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A462" s="2">
         <v>2961</v>
       </c>
@@ -25824,7 +25827,7 @@
         <v>709.17100000000005</v>
       </c>
     </row>
-    <row r="463" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A463" s="2">
         <v>2960</v>
       </c>
@@ -25877,7 +25880,7 @@
         <v>221.61600000000001</v>
       </c>
     </row>
-    <row r="464" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A464" s="2">
         <v>2958</v>
       </c>
@@ -25924,7 +25927,7 @@
         <v>102.4</v>
       </c>
     </row>
-    <row r="465" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A465" s="2">
         <v>2956</v>
       </c>
@@ -25971,7 +25974,7 @@
         <v>102.4</v>
       </c>
     </row>
-    <row r="466" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A466" s="2">
         <v>2951</v>
       </c>
@@ -26024,7 +26027,7 @@
         <v>221.393</v>
       </c>
     </row>
-    <row r="467" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A467" s="2">
         <v>2950</v>
       </c>
@@ -26077,7 +26080,7 @@
         <v>221.393</v>
       </c>
     </row>
-    <row r="468" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A468" s="2">
         <v>2947</v>
       </c>
@@ -26130,7 +26133,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="469" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A469" s="2">
         <v>2946</v>
       </c>
@@ -26183,7 +26186,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="470" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A470" s="2">
         <v>2942</v>
       </c>
@@ -26236,7 +26239,7 @@
         <v>221.393</v>
       </c>
     </row>
-    <row r="471" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A471" s="2">
         <v>2937</v>
       </c>
@@ -26289,7 +26292,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="472" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A472" s="2">
         <v>2936</v>
       </c>
@@ -26342,7 +26345,7 @@
         <v>10.24</v>
       </c>
     </row>
-    <row r="473" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A473" s="2">
         <v>2934</v>
       </c>
@@ -26395,7 +26398,7 @@
         <v>89.221000000000004</v>
       </c>
     </row>
-    <row r="474" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A474" s="2">
         <v>2933</v>
       </c>
@@ -26448,7 +26451,7 @@
         <v>44.610999999999997</v>
       </c>
     </row>
-    <row r="475" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A475" s="2">
         <v>2935</v>
       </c>
@@ -26501,7 +26504,7 @@
         <v>88.468000000000004</v>
       </c>
     </row>
-    <row r="476" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A476" s="2">
         <v>2929</v>
       </c>
@@ -26554,7 +26557,7 @@
         <v>92.891999999999996</v>
       </c>
     </row>
-    <row r="477" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A477" s="2">
         <v>2927</v>
       </c>
@@ -26607,7 +26610,7 @@
         <v>88.468000000000004</v>
       </c>
     </row>
-    <row r="478" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A478" s="2">
         <v>2926</v>
       </c>
@@ -26660,7 +26663,7 @@
         <v>83.914000000000001</v>
       </c>
     </row>
-    <row r="479" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A479" s="2">
         <v>2924</v>
       </c>
@@ -26713,7 +26716,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="480" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A480" s="2">
         <v>2922</v>
       </c>
@@ -26766,7 +26769,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="481" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A481" s="2">
         <v>2920</v>
       </c>
@@ -26819,7 +26822,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="482" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A482" s="2">
         <v>2918</v>
       </c>
@@ -26872,7 +26875,7 @@
         <v>2649.9140000000002</v>
       </c>
     </row>
-    <row r="483" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A483" s="2">
         <v>2907</v>
       </c>
@@ -26925,7 +26928,7 @@
         <v>21.512</v>
       </c>
     </row>
-    <row r="484" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A484" s="2">
         <v>2906</v>
       </c>
@@ -26978,7 +26981,7 @@
         <v>86.046000000000006</v>
       </c>
     </row>
-    <row r="485" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A485" s="2">
         <v>2905</v>
       </c>
@@ -27031,7 +27034,7 @@
         <v>129.06899999999999</v>
       </c>
     </row>
-    <row r="486" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A486" s="2">
         <v>2903</v>
       </c>
@@ -27084,7 +27087,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="487" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A487" s="2">
         <v>2901</v>
       </c>
@@ -27137,7 +27140,7 @@
         <v>5.12</v>
       </c>
     </row>
-    <row r="488" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A488" s="2">
         <v>2899</v>
       </c>
@@ -27190,7 +27193,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="489" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A489" s="2">
         <v>2897</v>
       </c>
@@ -27243,7 +27246,7 @@
         <v>81.92</v>
       </c>
     </row>
-    <row r="490" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A490" s="2">
         <v>2891</v>
       </c>
@@ -27296,7 +27299,7 @@
         <v>86.046000000000006</v>
       </c>
     </row>
-    <row r="491" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A491" s="2">
         <v>2885</v>
       </c>
@@ -27349,7 +27352,7 @@
         <v>110.373</v>
       </c>
     </row>
-    <row r="492" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A492" s="2">
         <v>2884</v>
       </c>
@@ -27402,7 +27405,7 @@
         <v>220.745</v>
       </c>
     </row>
-    <row r="493" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A493" s="2">
         <v>2882</v>
       </c>
@@ -27455,7 +27458,7 @@
         <v>5297.8860000000004</v>
       </c>
     </row>
-    <row r="494" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A494" s="2">
         <v>2881</v>
       </c>
@@ -27508,7 +27511,7 @@
         <v>66.224000000000004</v>
       </c>
     </row>
-    <row r="495" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A495" s="2">
         <v>2879</v>
       </c>
@@ -27561,7 +27564,7 @@
         <v>88.298000000000002</v>
       </c>
     </row>
-    <row r="496" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A496" s="2">
         <v>2877</v>
       </c>
@@ -27614,7 +27617,7 @@
         <v>470.72</v>
       </c>
     </row>
-    <row r="497" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A497" s="2">
         <v>2871</v>
       </c>
@@ -27667,7 +27670,7 @@
         <v>20.48</v>
       </c>
     </row>
-    <row r="498" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A498" s="2">
         <v>2869</v>
       </c>
@@ -27720,7 +27723,7 @@
         <v>263.06</v>
       </c>
     </row>
-    <row r="499" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A499" s="2">
         <v>2867</v>
       </c>
@@ -27773,7 +27776,7 @@
         <v>5.12</v>
       </c>
     </row>
-    <row r="500" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A500" s="2">
         <v>2860</v>
       </c>
@@ -27826,7 +27829,7 @@
         <v>66.066000000000003</v>
       </c>
     </row>
-    <row r="501" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A501" s="2">
         <v>2859</v>
       </c>
@@ -27879,7 +27882,7 @@
         <v>220.21899999999999</v>
       </c>
     </row>
-    <row r="502" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A502" s="2">
         <v>2858</v>
       </c>
@@ -27932,7 +27935,7 @@
         <v>132.131</v>
       </c>
     </row>
-    <row r="503" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A503" s="2">
         <v>2854</v>
       </c>
@@ -27985,7 +27988,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="504" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A504" s="2">
         <v>2853</v>
       </c>
@@ -28038,7 +28041,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="505" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A505" s="2">
         <v>2852</v>
       </c>
@@ -28091,7 +28094,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="506" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A506" s="2">
         <v>2851</v>
       </c>
@@ -28144,7 +28147,7 @@
         <v>110.10899999999999</v>
       </c>
     </row>
-    <row r="507" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A507" s="2">
         <v>2850</v>
       </c>
@@ -28197,7 +28200,7 @@
         <v>220.21899999999999</v>
       </c>
     </row>
-    <row r="508" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A508" s="2">
         <v>2840</v>
       </c>
@@ -28250,7 +28253,7 @@
         <v>21.965</v>
       </c>
     </row>
-    <row r="509" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A509" s="2">
         <v>2839</v>
       </c>
@@ -28303,7 +28306,7 @@
         <v>21.965</v>
       </c>
     </row>
-    <row r="510" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A510" s="2">
         <v>2838</v>
       </c>
@@ -28356,7 +28359,7 @@
         <v>21.965</v>
       </c>
     </row>
-    <row r="511" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A511" s="2">
         <v>2827</v>
       </c>
@@ -28409,7 +28412,7 @@
         <v>43.517000000000003</v>
       </c>
     </row>
-    <row r="512" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A512" s="2">
         <v>2824</v>
       </c>
@@ -28462,7 +28465,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="513" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A513" s="2">
         <v>2823</v>
       </c>
@@ -28515,7 +28518,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="514" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A514" s="2">
         <v>2820</v>
       </c>
@@ -28568,7 +28571,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="515" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A515" s="2">
         <v>2816</v>
       </c>
@@ -28621,7 +28624,7 @@
         <v>21.759</v>
       </c>
     </row>
-    <row r="516" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A516" s="2">
         <v>2814</v>
       </c>
@@ -28674,7 +28677,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="517" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A517" s="2">
         <v>2812</v>
       </c>
@@ -28727,7 +28730,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="518" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A518" s="2">
         <v>2811</v>
       </c>
@@ -28780,7 +28783,7 @@
         <v>44.06</v>
       </c>
     </row>
-    <row r="519" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A519" s="2">
         <v>2807</v>
       </c>
@@ -28833,7 +28836,7 @@
         <v>1321.799</v>
       </c>
     </row>
-    <row r="520" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A520" s="2">
         <v>2805</v>
       </c>
@@ -28886,7 +28889,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="521" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A521" s="2">
         <v>2804</v>
       </c>
@@ -28939,7 +28942,7 @@
         <v>15.36</v>
       </c>
     </row>
-    <row r="522" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A522" s="2">
         <v>2803</v>
       </c>
@@ -28992,7 +28995,7 @@
         <v>5.12</v>
       </c>
     </row>
-    <row r="523" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A523" s="2">
         <v>2801</v>
       </c>
@@ -29045,7 +29048,7 @@
         <v>35.840000000000003</v>
       </c>
     </row>
-    <row r="524" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A524" s="2">
         <v>2799</v>
       </c>
@@ -29098,7 +29101,7 @@
         <v>5.12</v>
       </c>
     </row>
-    <row r="525" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A525" s="2">
         <v>2797</v>
       </c>
@@ -29151,7 +29154,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="526" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A526" s="2">
         <v>2790</v>
       </c>
@@ -29204,7 +29207,7 @@
         <v>44.06</v>
       </c>
     </row>
-    <row r="527" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A527" s="2">
         <v>2788</v>
       </c>
@@ -29257,7 +29260,7 @@
         <v>881.19899999999996</v>
       </c>
     </row>
-    <row r="528" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A528" s="2">
         <v>2782</v>
       </c>
@@ -29310,7 +29313,7 @@
         <v>87.358000000000004</v>
       </c>
     </row>
-    <row r="529" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A529" s="2">
         <v>2780</v>
       </c>
@@ -29363,7 +29366,7 @@
         <v>655.18899999999996</v>
       </c>
     </row>
-    <row r="530" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A530" s="2">
         <v>2779</v>
       </c>
@@ -29416,7 +29419,7 @@
         <v>87.358000000000004</v>
       </c>
     </row>
-    <row r="531" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A531" s="2">
         <v>2778</v>
       </c>
@@ -29469,7 +29472,7 @@
         <v>87.358000000000004</v>
       </c>
     </row>
-    <row r="532" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A532" s="2">
         <v>2776</v>
       </c>
@@ -29522,7 +29525,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="533" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A533" s="2">
         <v>2774</v>
       </c>
@@ -29575,7 +29578,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="534" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A534" s="2">
         <v>2772</v>
       </c>
@@ -29628,7 +29631,7 @@
         <v>20.48</v>
       </c>
     </row>
-    <row r="535" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A535" s="2">
         <v>2771</v>
       </c>
@@ -29681,7 +29684,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="536" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A536" s="2">
         <v>2767</v>
       </c>
@@ -29734,7 +29737,7 @@
         <v>436.79199999999997</v>
       </c>
     </row>
-    <row r="537" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A537" s="2">
         <v>2765</v>
       </c>
@@ -29787,7 +29790,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="538" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A538" s="2">
         <v>2764</v>
       </c>
@@ -29840,7 +29843,7 @@
         <v>10.24</v>
       </c>
     </row>
-    <row r="539" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A539" s="2">
         <v>2761</v>
       </c>
@@ -29893,7 +29896,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="540" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A540" s="2">
         <v>2760</v>
       </c>
@@ -29946,7 +29949,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="541" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A541" s="2">
         <v>2759</v>
       </c>
@@ -29999,7 +30002,7 @@
         <v>87.358000000000004</v>
       </c>
     </row>
-    <row r="542" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A542" s="2">
         <v>2758</v>
       </c>
@@ -30052,7 +30055,7 @@
         <v>5.12</v>
       </c>
     </row>
-    <row r="543" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A543" s="2">
         <v>2757</v>
       </c>
@@ -30105,7 +30108,7 @@
         <v>109.107</v>
       </c>
     </row>
-    <row r="544" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A544" s="2">
         <v>2756</v>
       </c>
@@ -30158,7 +30161,7 @@
         <v>218.214</v>
       </c>
     </row>
-    <row r="545" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A545" s="2">
         <v>2754</v>
       </c>
@@ -30211,7 +30214,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="546" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A546" s="2">
         <v>2753</v>
       </c>
@@ -30264,7 +30267,7 @@
         <v>43.643000000000001</v>
       </c>
     </row>
-    <row r="547" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A547" s="2">
         <v>2746</v>
       </c>
@@ -30317,7 +30320,7 @@
         <v>218.214</v>
       </c>
     </row>
-    <row r="548" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A548" s="2">
         <v>2745</v>
       </c>
@@ -30370,7 +30373,7 @@
         <v>436.428</v>
       </c>
     </row>
-    <row r="549" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A549" s="2">
         <v>2740</v>
       </c>
@@ -30423,7 +30426,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="550" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A550" s="2">
         <v>2738</v>
       </c>
@@ -30476,7 +30479,7 @@
         <v>10.24</v>
       </c>
     </row>
-    <row r="551" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A551" s="2">
         <v>2735</v>
       </c>
@@ -30529,7 +30532,7 @@
         <v>2170.192</v>
       </c>
     </row>
-    <row r="552" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A552" s="2">
         <v>2734</v>
       </c>
@@ -30582,7 +30585,7 @@
         <v>434.03800000000001</v>
       </c>
     </row>
-    <row r="553" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A553" s="2">
         <v>2732</v>
       </c>
@@ -30635,7 +30638,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="554" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A554" s="2">
         <v>2730</v>
       </c>
@@ -30688,7 +30691,7 @@
         <v>434.03800000000001</v>
       </c>
     </row>
-    <row r="555" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A555" s="2">
         <v>2729</v>
       </c>
@@ -30741,7 +30744,7 @@
         <v>217.01900000000001</v>
       </c>
     </row>
-    <row r="556" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A556" s="2">
         <v>2727</v>
       </c>
@@ -30794,7 +30797,7 @@
         <v>434.03800000000001</v>
       </c>
     </row>
-    <row r="557" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A557" s="2">
         <v>2725</v>
       </c>
@@ -30847,7 +30850,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="558" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A558" s="2">
         <v>2720</v>
       </c>
@@ -30900,7 +30903,7 @@
         <v>414.43599999999998</v>
       </c>
     </row>
-    <row r="559" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A559" s="2">
         <v>2718</v>
       </c>
@@ -30953,7 +30956,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="560" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A560" s="2">
         <v>2716</v>
       </c>
@@ -31006,7 +31009,7 @@
         <v>1243.309</v>
       </c>
     </row>
-    <row r="561" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A561" s="2">
         <v>2689</v>
       </c>
@@ -31059,7 +31062,7 @@
         <v>86.97</v>
       </c>
     </row>
-    <row r="562" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A562" s="2">
         <v>2693</v>
       </c>
@@ -31112,7 +31115,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="563" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A563" s="2">
         <v>2687</v>
       </c>
@@ -31165,7 +31168,7 @@
         <v>5203.1139999999996</v>
       </c>
     </row>
-    <row r="564" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A564" s="2">
         <v>2686</v>
       </c>
@@ -31218,7 +31221,7 @@
         <v>86.718999999999994</v>
       </c>
     </row>
-    <row r="565" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A565" s="2">
         <v>2685</v>
       </c>
@@ -31271,7 +31274,7 @@
         <v>433.59300000000002</v>
       </c>
     </row>
-    <row r="566" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A566" s="2">
         <v>2684</v>
       </c>
@@ -31324,7 +31327,7 @@
         <v>433.59300000000002</v>
       </c>
     </row>
-    <row r="567" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A567" s="2">
         <v>2683</v>
       </c>
@@ -31377,7 +31380,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="568" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A568" s="2">
         <v>2682</v>
       </c>
@@ -31430,7 +31433,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="569" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A569" s="2">
         <v>2679</v>
       </c>
@@ -31483,7 +31486,7 @@
         <v>85.486999999999995</v>
       </c>
     </row>
-    <row r="570" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A570" s="2">
         <v>2676</v>
       </c>
@@ -31536,7 +31539,7 @@
         <v>85.414000000000001</v>
       </c>
     </row>
-    <row r="571" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A571" s="2">
         <v>2667</v>
       </c>
@@ -31589,7 +31592,7 @@
         <v>312.32</v>
       </c>
     </row>
-    <row r="572" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A572" s="2">
         <v>2665</v>
       </c>
@@ -31642,7 +31645,7 @@
         <v>885.76</v>
       </c>
     </row>
-    <row r="573" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A573" s="2">
         <v>2664</v>
       </c>
@@ -31695,7 +31698,7 @@
         <v>345.54599999999999</v>
       </c>
     </row>
-    <row r="574" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A574" s="2">
         <v>2658</v>
       </c>
@@ -31748,7 +31751,7 @@
         <v>1295.19</v>
       </c>
     </row>
-    <row r="575" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A575" s="2">
         <v>2653</v>
       </c>
@@ -31801,7 +31804,7 @@
         <v>86.346000000000004</v>
       </c>
     </row>
-    <row r="576" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A576" s="2">
         <v>2652</v>
       </c>
@@ -31854,7 +31857,7 @@
         <v>2590.3809999999999</v>
       </c>
     </row>
-    <row r="577" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A577" s="2">
         <v>2649</v>
       </c>
@@ -31907,7 +31910,7 @@
         <v>1719.63</v>
       </c>
     </row>
-    <row r="578" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A578" s="2">
         <v>2648</v>
       </c>
@@ -31960,7 +31963,7 @@
         <v>859.81500000000005</v>
       </c>
     </row>
-    <row r="579" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A579" s="2">
         <v>2642</v>
       </c>
@@ -32013,7 +32016,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="580" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A580" s="2">
         <v>2640</v>
       </c>
@@ -32066,7 +32069,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="581" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A581" s="2">
         <v>2638</v>
       </c>
@@ -32119,7 +32122,7 @@
         <v>1889.8119999999999</v>
       </c>
     </row>
-    <row r="582" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A582" s="2">
         <v>2635</v>
       </c>
@@ -32172,7 +32175,7 @@
         <v>30.72</v>
       </c>
     </row>
-    <row r="583" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A583" s="2">
         <v>2633</v>
       </c>
@@ -32225,7 +32228,7 @@
         <v>10.24</v>
       </c>
     </row>
-    <row r="584" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A584" s="2">
         <v>2631</v>
       </c>
@@ -32278,7 +32281,7 @@
         <v>40.96</v>
       </c>
     </row>
-    <row r="585" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A585" s="2">
         <v>2629</v>
       </c>
@@ -32331,7 +32334,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="586" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A586" s="2">
         <v>2627</v>
       </c>
@@ -32384,7 +32387,7 @@
         <v>30.72</v>
       </c>
     </row>
-    <row r="587" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A587" s="2">
         <v>2625</v>
       </c>
@@ -32437,7 +32440,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="588" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A588" s="2">
         <v>2624</v>
       </c>
@@ -32490,7 +32493,7 @@
         <v>86.54</v>
       </c>
     </row>
-    <row r="589" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A589" s="2">
         <v>2623</v>
       </c>
@@ -32543,7 +32546,7 @@
         <v>86.54</v>
       </c>
     </row>
-    <row r="590" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A590" s="2">
         <v>2622</v>
       </c>
@@ -32596,7 +32599,7 @@
         <v>129.81100000000001</v>
       </c>
     </row>
-    <row r="591" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A591" s="2">
         <v>2615</v>
       </c>
@@ -32649,7 +32652,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="592" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A592" s="2">
         <v>2614</v>
       </c>
@@ -32702,7 +32705,7 @@
         <v>46.08</v>
       </c>
     </row>
-    <row r="593" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A593" s="2">
         <v>2613</v>
       </c>
@@ -32755,7 +32758,7 @@
         <v>20.48</v>
       </c>
     </row>
-    <row r="594" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A594" s="2">
         <v>2612</v>
       </c>
@@ -32808,7 +32811,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="595" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A595" s="2">
         <v>2611</v>
       </c>
@@ -32861,7 +32864,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="596" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A596" s="2">
         <v>2610</v>
       </c>
@@ -32914,7 +32917,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="597" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A597" s="2">
         <v>2609</v>
       </c>
@@ -32967,7 +32970,7 @@
         <v>43.27</v>
       </c>
     </row>
-    <row r="598" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A598" s="2">
         <v>2608</v>
       </c>
@@ -33020,7 +33023,7 @@
         <v>346.16199999999998</v>
       </c>
     </row>
-    <row r="599" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A599" s="2">
         <v>2607</v>
       </c>
@@ -33073,7 +33076,7 @@
         <v>692.32299999999998</v>
       </c>
     </row>
-    <row r="600" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A600" s="2">
         <v>2592</v>
       </c>
@@ -33126,7 +33129,7 @@
         <v>86.013999999999996</v>
       </c>
     </row>
-    <row r="601" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A601" s="2">
         <v>2589</v>
       </c>
@@ -33179,7 +33182,7 @@
         <v>860.13900000000001</v>
       </c>
     </row>
-    <row r="602" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A602" s="2">
         <v>2588</v>
       </c>
@@ -33232,7 +33235,7 @@
         <v>1720.278</v>
       </c>
     </row>
-    <row r="603" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A603" s="2">
         <v>2587</v>
       </c>
@@ -33285,7 +33288,7 @@
         <v>5.12</v>
       </c>
     </row>
-    <row r="604" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A604" s="2">
         <v>2586</v>
       </c>
@@ -33338,7 +33341,7 @@
         <v>10.24</v>
       </c>
     </row>
-    <row r="605" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A605" s="2">
         <v>2585</v>
       </c>
@@ -33391,7 +33394,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="606" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A606" s="2">
         <v>2584</v>
       </c>
@@ -33444,7 +33447,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="607" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A607" s="2">
         <v>2583</v>
       </c>
@@ -33497,7 +33500,7 @@
         <v>129.02099999999999</v>
       </c>
     </row>
-    <row r="608" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A608" s="2">
         <v>2580</v>
       </c>
@@ -33550,7 +33553,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="609" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A609" s="2">
         <v>2579</v>
       </c>
@@ -33603,7 +33606,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="610" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A610" s="2">
         <v>2575</v>
       </c>
@@ -33656,7 +33659,7 @@
         <v>21.503</v>
       </c>
     </row>
-    <row r="611" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A611" s="2">
         <v>2570</v>
       </c>
@@ -33709,7 +33712,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="612" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A612" s="2">
         <v>2569</v>
       </c>
@@ -33762,7 +33765,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="613" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A613" s="2">
         <v>2568</v>
       </c>
@@ -33815,7 +33818,7 @@
         <v>344.05599999999998</v>
       </c>
     </row>
-    <row r="614" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A614" s="2">
         <v>2567</v>
       </c>
@@ -33868,7 +33871,7 @@
         <v>215.035</v>
       </c>
     </row>
-    <row r="615" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A615" s="2">
         <v>2566</v>
       </c>
@@ -33921,7 +33924,7 @@
         <v>21.503</v>
       </c>
     </row>
-    <row r="616" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A616" s="2">
         <v>2565</v>
       </c>
@@ -33974,7 +33977,7 @@
         <v>430.07</v>
       </c>
     </row>
-    <row r="617" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A617" s="2">
         <v>2564</v>
       </c>
@@ -34027,7 +34030,7 @@
         <v>43.006999999999998</v>
       </c>
     </row>
-    <row r="618" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A618" s="2">
         <v>2563</v>
       </c>
@@ -34080,7 +34083,7 @@
         <v>43.006999999999998</v>
       </c>
     </row>
-    <row r="619" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A619" s="2">
         <v>2562</v>
       </c>
@@ -34133,7 +34136,7 @@
         <v>15.36</v>
       </c>
     </row>
-    <row r="620" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A620" s="2">
         <v>2561</v>
       </c>
@@ -34186,7 +34189,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="621" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A621" s="2">
         <v>2560</v>
       </c>
@@ -34239,7 +34242,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="622" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A622" s="2">
         <v>2559</v>
       </c>
@@ -34292,7 +34295,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="623" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A623" s="2">
         <v>2558</v>
       </c>
@@ -34345,7 +34348,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="624" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A624" s="2">
         <v>2557</v>
       </c>
@@ -34398,7 +34401,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="625" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A625" s="2">
         <v>2556</v>
       </c>
@@ -34451,7 +34454,7 @@
         <v>42.744</v>
       </c>
     </row>
-    <row r="626" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A626" s="2">
         <v>2555</v>
       </c>
@@ -34504,7 +34507,7 @@
         <v>85.486999999999995</v>
       </c>
     </row>
-    <row r="627" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A627" s="2">
         <v>2554</v>
       </c>
@@ -34557,7 +34560,7 @@
         <v>106.85899999999999</v>
       </c>
     </row>
-    <row r="628" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A628" s="2">
         <v>2553</v>
       </c>
@@ -34610,7 +34613,7 @@
         <v>106.85899999999999</v>
       </c>
     </row>
-    <row r="629" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A629" s="2">
         <v>2552</v>
       </c>
@@ -34663,7 +34666,7 @@
         <v>128.23099999999999</v>
       </c>
     </row>
-    <row r="630" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A630" s="2">
         <v>2549</v>
       </c>
@@ -34716,7 +34719,7 @@
         <v>428.08499999999998</v>
       </c>
     </row>
-    <row r="631" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A631" s="2">
         <v>2548</v>
       </c>
@@ -34769,7 +34772,7 @@
         <v>642.12699999999995</v>
       </c>
     </row>
-    <row r="632" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A632" s="2">
         <v>2547</v>
       </c>
@@ -34822,7 +34825,7 @@
         <v>214.042</v>
       </c>
     </row>
-    <row r="633" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A633" s="2">
         <v>2546</v>
       </c>
@@ -34875,7 +34878,7 @@
         <v>428.08499999999998</v>
       </c>
     </row>
-    <row r="634" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A634" s="2">
         <v>2545</v>
       </c>
@@ -34928,7 +34931,7 @@
         <v>428.08499999999998</v>
       </c>
     </row>
-    <row r="635" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A635" s="2">
         <v>2544</v>
       </c>
@@ -34981,7 +34984,7 @@
         <v>599.31899999999996</v>
       </c>
     </row>
-    <row r="636" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A636" s="2">
         <v>2543</v>
       </c>
@@ -35034,7 +35037,7 @@
         <v>428.08499999999998</v>
       </c>
     </row>
-    <row r="637" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A637" s="2">
         <v>2540</v>
       </c>
@@ -35087,7 +35090,7 @@
         <v>20.48</v>
       </c>
     </row>
-    <row r="638" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A638" s="2">
         <v>2539</v>
       </c>
@@ -35140,7 +35143,7 @@
         <v>214.042</v>
       </c>
     </row>
-    <row r="639" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A639" s="2">
         <v>2538</v>
       </c>
@@ -35193,7 +35196,7 @@
         <v>428.08499999999998</v>
       </c>
     </row>
-    <row r="640" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A640" s="2">
         <v>2537</v>
       </c>
@@ -35246,7 +35249,7 @@
         <v>342.46800000000002</v>
       </c>
     </row>
-    <row r="641" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A641" s="2">
         <v>2536</v>
       </c>
@@ -35299,7 +35302,7 @@
         <v>20.48</v>
       </c>
     </row>
-    <row r="642" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A642" s="2">
         <v>2533</v>
       </c>
@@ -35352,7 +35355,7 @@
         <v>214.97399999999999</v>
       </c>
     </row>
-    <row r="643" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A643" s="2">
         <v>2532</v>
       </c>
@@ -35405,7 +35408,7 @@
         <v>257.96899999999999</v>
       </c>
     </row>
-    <row r="644" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A644" s="2">
         <v>2531</v>
       </c>
@@ -35458,7 +35461,7 @@
         <v>171.97900000000001</v>
       </c>
     </row>
-    <row r="645" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A645" s="2">
         <v>2525</v>
       </c>
@@ -35511,7 +35514,7 @@
         <v>43.107999999999997</v>
       </c>
     </row>
-    <row r="646" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A646" s="2">
         <v>2524</v>
       </c>
@@ -35564,7 +35567,7 @@
         <v>172.43299999999999</v>
       </c>
     </row>
-    <row r="647" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A647" s="2">
         <v>2523</v>
       </c>
@@ -35617,7 +35620,7 @@
         <v>172.125</v>
       </c>
     </row>
-    <row r="648" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A648" s="2">
         <v>2521</v>
       </c>
@@ -35670,7 +35673,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="649" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A649" s="2">
         <v>2520</v>
       </c>
@@ -35723,7 +35726,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="650" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A650" s="2">
         <v>2517</v>
       </c>
@@ -35776,7 +35779,7 @@
         <v>43.335000000000001</v>
       </c>
     </row>
-    <row r="651" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A651" s="2">
         <v>2516</v>
       </c>
@@ -35829,7 +35832,7 @@
         <v>1906.741</v>
       </c>
     </row>
-    <row r="652" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A652" s="2">
         <v>2514</v>
       </c>
@@ -35882,7 +35885,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="653" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A653" s="2">
         <v>2509</v>
       </c>
@@ -35935,7 +35938,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="654" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A654" s="2">
         <v>2508</v>
       </c>
@@ -35988,7 +35991,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="655" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A655" s="2">
         <v>2502</v>
       </c>
@@ -36041,7 +36044,7 @@
         <v>202.6</v>
       </c>
     </row>
-    <row r="656" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A656" s="2">
         <v>2496</v>
       </c>
@@ -36094,7 +36097,7 @@
         <v>60.2</v>
       </c>
     </row>
-    <row r="657" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A657" s="2">
         <v>2493</v>
       </c>
@@ -36147,7 +36150,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="658" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A658" s="2">
         <v>2492</v>
       </c>
@@ -36200,7 +36203,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="659" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A659" s="2">
         <v>2646</v>
       </c>
@@ -36253,7 +36256,7 @@
         <v>15.36</v>
       </c>
     </row>
-    <row r="660" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A660" s="2">
         <v>2483</v>
       </c>
@@ -36306,7 +36309,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="661" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A661" s="2">
         <v>2482</v>
       </c>
@@ -36359,7 +36362,7 @@
         <v>76.8</v>
       </c>
     </row>
-    <row r="662" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A662" s="2">
         <v>2481</v>
       </c>
@@ -36412,7 +36415,7 @@
         <v>76.8</v>
       </c>
     </row>
-    <row r="663" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A663" s="2">
         <v>2466</v>
       </c>
@@ -36465,7 +36468,7 @@
         <v>35.840000000000003</v>
       </c>
     </row>
-    <row r="664" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A664" s="2">
         <v>2465</v>
       </c>
@@ -36518,7 +36521,7 @@
         <v>20.48</v>
       </c>
     </row>
-    <row r="665" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A665" s="2">
         <v>2464</v>
       </c>
@@ -36571,7 +36574,7 @@
         <v>5.12</v>
       </c>
     </row>
-    <row r="666" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A666" s="2">
         <v>2453</v>
       </c>
@@ -36624,7 +36627,7 @@
         <v>133.12</v>
       </c>
     </row>
-    <row r="667" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A667" s="2">
         <v>2452</v>
       </c>
@@ -36677,7 +36680,7 @@
         <v>87.245000000000005</v>
       </c>
     </row>
-    <row r="668" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A668" s="2">
         <v>2451</v>
       </c>
@@ -36730,7 +36733,7 @@
         <v>87.245000000000005</v>
       </c>
     </row>
-    <row r="669" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A669" s="2">
         <v>2450</v>
       </c>
@@ -36783,7 +36786,7 @@
         <v>87.245000000000005</v>
       </c>
     </row>
-    <row r="670" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A670" s="2">
         <v>2449</v>
       </c>
@@ -36836,7 +36839,7 @@
         <v>87.245000000000005</v>
       </c>
     </row>
-    <row r="671" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A671" s="2">
         <v>2447</v>
       </c>
@@ -36889,7 +36892,7 @@
         <v>87.245000000000005</v>
       </c>
     </row>
-    <row r="672" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A672" s="2">
         <v>2446</v>
       </c>
@@ -36942,7 +36945,7 @@
         <v>174.49</v>
       </c>
     </row>
-    <row r="673" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A673" s="2">
         <v>2445</v>
       </c>
@@ -36995,7 +36998,7 @@
         <v>204.8</v>
       </c>
     </row>
-    <row r="674" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A674" s="2">
         <v>2444</v>
       </c>
@@ -37048,7 +37051,7 @@
         <v>87.245000000000005</v>
       </c>
     </row>
-    <row r="675" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A675" s="2">
         <v>2443</v>
       </c>
@@ -37101,7 +37104,7 @@
         <v>87.245000000000005</v>
       </c>
     </row>
-    <row r="676" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A676" s="2">
         <v>2441</v>
       </c>
@@ -37154,7 +37157,7 @@
         <v>10.24</v>
       </c>
     </row>
-    <row r="677" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A677" s="2">
         <v>2440</v>
       </c>
@@ -37207,7 +37210,7 @@
         <v>10.24</v>
       </c>
     </row>
-    <row r="678" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A678" s="2">
         <v>2439</v>
       </c>
@@ -37260,7 +37263,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="679" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A679" s="2">
         <v>2438</v>
       </c>
@@ -37313,7 +37316,7 @@
         <v>66.56</v>
       </c>
     </row>
-    <row r="680" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A680" s="2">
         <v>2437</v>
       </c>
@@ -37366,7 +37369,7 @@
         <v>122.88</v>
       </c>
     </row>
-    <row r="681" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A681" s="2">
         <v>2424</v>
       </c>
@@ -37419,7 +37422,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="682" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A682" s="2">
         <v>2647</v>
       </c>
@@ -37472,7 +37475,7 @@
         <v>10.24</v>
       </c>
     </row>
-    <row r="683" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A683" s="2">
         <v>2421</v>
       </c>
@@ -37525,7 +37528,7 @@
         <v>803.8</v>
       </c>
     </row>
-    <row r="684" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A684" s="2">
         <v>2420</v>
       </c>
@@ -37578,7 +37581,7 @@
         <v>719.52</v>
       </c>
     </row>
-    <row r="685" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A685" s="2">
         <v>2418</v>
       </c>
@@ -37631,7 +37634,7 @@
         <v>10.24</v>
       </c>
     </row>
-    <row r="686" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A686" s="2">
         <v>2417</v>
       </c>
@@ -37684,7 +37687,7 @@
         <v>5.12</v>
       </c>
     </row>
-    <row r="687" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A687" s="2">
         <v>2416</v>
       </c>
@@ -37737,7 +37740,7 @@
         <v>20.48</v>
       </c>
     </row>
-    <row r="688" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A688" s="2">
         <v>2415</v>
       </c>
@@ -37790,7 +37793,7 @@
         <v>5.12</v>
       </c>
     </row>
-    <row r="689" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A689" s="2">
         <v>2414</v>
       </c>
@@ -37843,7 +37846,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="690" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A690" s="2">
         <v>2413</v>
       </c>
@@ -37896,7 +37899,7 @@
         <v>20.48</v>
       </c>
     </row>
-    <row r="691" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A691" s="2">
         <v>2411</v>
       </c>
@@ -37949,7 +37952,7 @@
         <v>15.36</v>
       </c>
     </row>
-    <row r="692" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A692" s="2">
         <v>2407</v>
       </c>
@@ -38002,7 +38005,7 @@
         <v>122.88</v>
       </c>
     </row>
-    <row r="693" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A693" s="2">
         <v>2405</v>
       </c>
@@ -38055,7 +38058,7 @@
         <v>682.14</v>
       </c>
     </row>
-    <row r="694" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A694" s="2">
         <v>2403</v>
       </c>
@@ -38108,7 +38111,7 @@
         <v>1754.075</v>
       </c>
     </row>
-    <row r="695" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A695" s="2">
         <v>2401</v>
       </c>
@@ -38161,7 +38164,7 @@
         <v>487.24299999999999</v>
       </c>
     </row>
-    <row r="696" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A696" s="2">
         <v>2400</v>
       </c>
@@ -38214,7 +38217,7 @@
         <v>265.76900000000001</v>
       </c>
     </row>
-    <row r="697" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A697" s="2">
         <v>2396</v>
       </c>
@@ -38267,7 +38270,7 @@
         <v>132.88399999999999</v>
       </c>
     </row>
-    <row r="698" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A698" s="2">
         <v>2397</v>
       </c>
@@ -38320,7 +38323,7 @@
         <v>88.241</v>
       </c>
     </row>
-    <row r="699" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A699" s="2">
         <v>2395</v>
       </c>
@@ -38373,7 +38376,7 @@
         <v>44.121000000000002</v>
       </c>
     </row>
-    <row r="700" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A700" s="2">
         <v>2391</v>
       </c>
@@ -38426,7 +38429,7 @@
         <v>132.36199999999999</v>
       </c>
     </row>
-    <row r="701" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A701" s="2">
         <v>2390</v>
       </c>
@@ -38479,7 +38482,7 @@
         <v>44.121000000000002</v>
       </c>
     </row>
-    <row r="702" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A702" s="2">
         <v>2389</v>
       </c>
@@ -38532,7 +38535,7 @@
         <v>88.241</v>
       </c>
     </row>
-    <row r="703" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A703" s="2">
         <v>2388</v>
       </c>
@@ -38585,7 +38588,7 @@
         <v>220.60400000000001</v>
       </c>
     </row>
-    <row r="704" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A704" s="2">
         <v>2387</v>
       </c>
@@ -38638,7 +38641,7 @@
         <v>220.60400000000001</v>
       </c>
     </row>
-    <row r="705" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A705" s="2">
         <v>2386</v>
       </c>
@@ -38691,7 +38694,7 @@
         <v>441.20699999999999</v>
       </c>
     </row>
-    <row r="706" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A706" s="2">
         <v>2385</v>
       </c>
@@ -38744,7 +38747,7 @@
         <v>882.41399999999999</v>
       </c>
     </row>
-    <row r="707" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A707" s="2">
         <v>2384</v>
       </c>
@@ -38797,7 +38800,7 @@
         <v>1323.6220000000001</v>
       </c>
     </row>
-    <row r="708" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A708" s="2">
         <v>2383</v>
       </c>
@@ -38850,7 +38853,7 @@
         <v>44.121000000000002</v>
       </c>
     </row>
-    <row r="709" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A709" s="2">
         <v>2382</v>
       </c>
@@ -38903,7 +38906,7 @@
         <v>110.30200000000001</v>
       </c>
     </row>
-    <row r="710" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A710" s="2">
         <v>2380</v>
       </c>
@@ -38956,7 +38959,7 @@
         <v>88.241</v>
       </c>
     </row>
-    <row r="711" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A711" s="2">
         <v>2379</v>
       </c>
@@ -39009,7 +39012,7 @@
         <v>88.241</v>
       </c>
     </row>
-    <row r="712" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A712" s="2">
         <v>2378</v>
       </c>
@@ -39062,7 +39065,7 @@
         <v>88.241</v>
       </c>
     </row>
-    <row r="713" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A713" s="2">
         <v>2377</v>
       </c>
@@ -39115,7 +39118,7 @@
         <v>121.33</v>
       </c>
     </row>
-    <row r="714" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A714" s="2">
         <v>2376</v>
       </c>
@@ -39168,7 +39171,7 @@
         <v>121.33</v>
       </c>
     </row>
-    <row r="715" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A715" s="2">
         <v>2375</v>
       </c>
@@ -39221,7 +39224,7 @@
         <v>15.36</v>
       </c>
     </row>
-    <row r="716" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A716" s="2">
         <v>2373</v>
       </c>
@@ -39274,7 +39277,7 @@
         <v>1779.5050000000001</v>
       </c>
     </row>
-    <row r="717" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A717" s="2">
         <v>2372</v>
       </c>
@@ -39327,7 +39330,7 @@
         <v>202.21600000000001</v>
       </c>
     </row>
-    <row r="718" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A718" s="2">
         <v>2371</v>
       </c>
@@ -39380,7 +39383,7 @@
         <v>161.773</v>
       </c>
     </row>
-    <row r="719" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A719" s="2">
         <v>2370</v>
       </c>
@@ -39433,7 +39436,7 @@
         <v>20.48</v>
       </c>
     </row>
-    <row r="720" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A720" s="2">
         <v>2368</v>
       </c>
@@ -39486,7 +39489,7 @@
         <v>66.186999999999998</v>
       </c>
     </row>
-    <row r="721" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A721" s="2">
         <v>2367</v>
       </c>
@@ -39539,7 +39542,7 @@
         <v>132.374</v>
       </c>
     </row>
-    <row r="722" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A722" s="2">
         <v>2366</v>
       </c>
@@ -39592,7 +39595,7 @@
         <v>220.624</v>
       </c>
     </row>
-    <row r="723" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A723" s="2">
         <v>2365</v>
       </c>
@@ -39645,7 +39648,7 @@
         <v>220.624</v>
       </c>
     </row>
-    <row r="724" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A724" s="2">
         <v>2364</v>
       </c>
@@ -39698,7 +39701,7 @@
         <v>10.24</v>
       </c>
     </row>
-    <row r="725" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A725" s="2">
         <v>2522</v>
       </c>
@@ -39751,7 +39754,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="726" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A726" s="2">
         <v>2337</v>
       </c>
@@ -39804,7 +39807,7 @@
         <v>88.055000000000007</v>
       </c>
     </row>
-    <row r="727" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A727" s="2">
         <v>2336</v>
       </c>
@@ -39857,7 +39860,7 @@
         <v>440.27499999999998</v>
       </c>
     </row>
-    <row r="728" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A728" s="2">
         <v>2335</v>
       </c>
@@ -39910,7 +39913,7 @@
         <v>30.72</v>
       </c>
     </row>
-    <row r="729" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A729" s="2">
         <v>2334</v>
       </c>
@@ -39963,7 +39966,7 @@
         <v>44.027999999999999</v>
       </c>
     </row>
-    <row r="730" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A730" s="2">
         <v>2333</v>
       </c>
@@ -40016,7 +40019,7 @@
         <v>44.027999999999999</v>
       </c>
     </row>
-    <row r="731" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A731" s="2">
         <v>2332</v>
       </c>
@@ -40069,7 +40072,7 @@
         <v>176.11</v>
       </c>
     </row>
-    <row r="732" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A732" s="2">
         <v>2330</v>
       </c>
@@ -40122,7 +40125,7 @@
         <v>131.536</v>
       </c>
     </row>
-    <row r="733" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A733" s="2">
         <v>2329</v>
       </c>
@@ -40175,7 +40178,7 @@
         <v>306.91699999999997</v>
       </c>
     </row>
-    <row r="734" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A734" s="2">
         <v>2323</v>
       </c>
@@ -40228,7 +40231,7 @@
         <v>43.844999999999999</v>
       </c>
     </row>
-    <row r="735" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A735" s="2">
         <v>2322</v>
       </c>
@@ -40281,7 +40284,7 @@
         <v>87.691000000000003</v>
       </c>
     </row>
-    <row r="736" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A736" s="2">
         <v>2321</v>
       </c>
@@ -40334,7 +40337,7 @@
         <v>175.381</v>
       </c>
     </row>
-    <row r="737" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A737" s="2">
         <v>2320</v>
       </c>
@@ -40387,7 +40390,7 @@
         <v>87.691000000000003</v>
       </c>
     </row>
-    <row r="738" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A738" s="2">
         <v>2319</v>
       </c>
@@ -40440,7 +40443,7 @@
         <v>219.227</v>
       </c>
     </row>
-    <row r="739" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A739" s="2">
         <v>2318</v>
       </c>
@@ -40493,7 +40496,7 @@
         <v>219.227</v>
       </c>
     </row>
-    <row r="740" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A740" s="2">
         <v>2317</v>
       </c>
@@ -40546,7 +40549,7 @@
         <v>219.227</v>
       </c>
     </row>
-    <row r="741" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A741" s="2">
         <v>2316</v>
       </c>
@@ -40599,7 +40602,7 @@
         <v>219.227</v>
       </c>
     </row>
-    <row r="742" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A742" s="2">
         <v>2315</v>
       </c>
@@ -40652,7 +40655,7 @@
         <v>219.227</v>
       </c>
     </row>
-    <row r="743" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A743" s="2">
         <v>2314</v>
       </c>
@@ -40705,7 +40708,7 @@
         <v>219.227</v>
       </c>
     </row>
-    <row r="744" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A744" s="2">
         <v>2313</v>
       </c>
@@ -40758,7 +40761,7 @@
         <v>604.16</v>
       </c>
     </row>
-    <row r="745" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A745" s="2">
         <v>2312</v>
       </c>
@@ -40811,7 +40814,7 @@
         <v>43.801000000000002</v>
       </c>
     </row>
-    <row r="746" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A746" s="2">
         <v>2311</v>
       </c>
@@ -40864,7 +40867,7 @@
         <v>438.00700000000001</v>
       </c>
     </row>
-    <row r="747" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A747" s="2">
         <v>2310</v>
       </c>
@@ -40917,7 +40920,7 @@
         <v>175.203</v>
       </c>
     </row>
-    <row r="748" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A748" s="2">
         <v>2308</v>
       </c>
@@ -40970,7 +40973,7 @@
         <v>43.801000000000002</v>
       </c>
     </row>
-    <row r="749" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A749" s="2">
         <v>2307</v>
       </c>
@@ -41023,7 +41026,7 @@
         <v>43.801000000000002</v>
       </c>
     </row>
-    <row r="750" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A750" s="2">
         <v>2306</v>
       </c>
@@ -41076,7 +41079,7 @@
         <v>43.801000000000002</v>
       </c>
     </row>
-    <row r="751" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A751" s="2">
         <v>2305</v>
       </c>
@@ -41129,7 +41132,7 @@
         <v>43.801000000000002</v>
       </c>
     </row>
-    <row r="752" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A752" s="2">
         <v>2362</v>
       </c>
@@ -41176,7 +41179,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="753" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A753" s="2">
         <v>2361</v>
       </c>
@@ -41223,7 +41226,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="754" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A754" s="2">
         <v>2304</v>
       </c>
@@ -41276,7 +41279,7 @@
         <v>65.846999999999994</v>
       </c>
     </row>
-    <row r="755" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A755" s="2">
         <v>2303</v>
       </c>
@@ -41329,7 +41332,7 @@
         <v>109.745</v>
       </c>
     </row>
-    <row r="756" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A756" s="2">
         <v>2302</v>
       </c>
@@ -41382,7 +41385,7 @@
         <v>263.38799999999998</v>
       </c>
     </row>
-    <row r="757" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A757" s="2">
         <v>2301</v>
       </c>
@@ -41435,7 +41438,7 @@
         <v>87.796000000000006</v>
       </c>
     </row>
-    <row r="758" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A758" s="2">
         <v>2300</v>
       </c>
@@ -41488,7 +41491,7 @@
         <v>263.38799999999998</v>
       </c>
     </row>
-    <row r="759" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A759" s="2">
         <v>2299</v>
       </c>
@@ -41541,7 +41544,7 @@
         <v>219.571</v>
       </c>
     </row>
-    <row r="760" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A760" s="2">
         <v>2297</v>
       </c>
@@ -41594,7 +41597,7 @@
         <v>43.789000000000001</v>
       </c>
     </row>
-    <row r="761" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A761" s="2">
         <v>2296</v>
       </c>
@@ -41647,7 +41650,7 @@
         <v>87.576999999999998</v>
       </c>
     </row>
-    <row r="762" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A762" s="2">
         <v>2294</v>
       </c>
@@ -41700,7 +41703,7 @@
         <v>1926.6990000000001</v>
       </c>
     </row>
-    <row r="763" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A763" s="2">
         <v>2292</v>
       </c>
@@ -41753,7 +41756,7 @@
         <v>87.593000000000004</v>
       </c>
     </row>
-    <row r="764" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A764" s="2">
         <v>2291</v>
       </c>
@@ -41806,7 +41809,7 @@
         <v>87.593000000000004</v>
       </c>
     </row>
-    <row r="765" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A765" s="2">
         <v>2290</v>
       </c>
@@ -41859,7 +41862,7 @@
         <v>87.593000000000004</v>
       </c>
     </row>
-    <row r="766" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A766" s="2">
         <v>2363</v>
       </c>
@@ -41912,7 +41915,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="767" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A767" s="2">
         <v>2287</v>
       </c>
@@ -41965,7 +41968,7 @@
         <v>20.48</v>
       </c>
     </row>
-    <row r="768" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A768" s="2">
         <v>2286</v>
       </c>
@@ -42018,7 +42021,7 @@
         <v>10.24</v>
       </c>
     </row>
-    <row r="769" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A769" s="2">
         <v>2282</v>
       </c>
@@ -42071,7 +42074,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="770" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A770" s="2">
         <v>2280</v>
       </c>
@@ -42124,7 +42127,7 @@
         <v>20.48</v>
       </c>
     </row>
-    <row r="771" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A771" s="2">
         <v>2279</v>
       </c>
@@ -42177,7 +42180,7 @@
         <v>87.253</v>
       </c>
     </row>
-    <row r="772" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A772" s="2">
         <v>2266</v>
       </c>
@@ -42230,7 +42233,7 @@
         <v>694.85</v>
       </c>
     </row>
-    <row r="773" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A773" s="2">
         <v>2265</v>
       </c>
@@ -42283,7 +42286,7 @@
         <v>78.171000000000006</v>
       </c>
     </row>
-    <row r="774" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A774" s="2">
         <v>2264</v>
       </c>
@@ -42336,7 +42339,7 @@
         <v>130.28399999999999</v>
       </c>
     </row>
-    <row r="775" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A775" s="2">
         <v>2259</v>
       </c>
@@ -42389,7 +42392,7 @@
         <v>15.36</v>
       </c>
     </row>
-    <row r="776" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A776" s="2">
         <v>2258</v>
       </c>
@@ -42442,7 +42445,7 @@
         <v>26.056999999999999</v>
       </c>
     </row>
-    <row r="777" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A777" s="2">
         <v>2257</v>
       </c>
@@ -42495,7 +42498,7 @@
         <v>60.798999999999999</v>
       </c>
     </row>
-    <row r="778" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A778" s="2">
         <v>2255</v>
       </c>
@@ -42548,7 +42551,7 @@
         <v>141.88</v>
       </c>
     </row>
-    <row r="779" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A779" s="2">
         <v>2253</v>
       </c>
@@ -42601,7 +42604,7 @@
         <v>86.855999999999995</v>
       </c>
     </row>
-    <row r="780" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A780" s="2">
         <v>2248</v>
       </c>
@@ -42654,7 +42657,7 @@
         <v>43.427999999999997</v>
       </c>
     </row>
-    <row r="781" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A781" s="2">
         <v>2247</v>
       </c>
@@ -42707,7 +42710,7 @@
         <v>347.42500000000001</v>
       </c>
     </row>
-    <row r="782" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A782" s="2">
         <v>2243</v>
       </c>
@@ -42738,8 +42741,8 @@
       <c r="M782" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="N782" s="2">
-        <v>4359</v>
+      <c r="N782" s="2" t="s">
+        <v>382</v>
       </c>
       <c r="O782" s="2" t="s">
         <v>57</v>
@@ -42754,7 +42757,7 @@
         <v>52.2</v>
       </c>
     </row>
-    <row r="783" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A783" s="2">
         <v>2242</v>
       </c>
@@ -42807,7 +42810,7 @@
         <v>433.18799999999999</v>
       </c>
     </row>
-    <row r="784" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A784" s="2">
         <v>2241</v>
       </c>
@@ -42860,7 +42863,7 @@
         <v>43.319000000000003</v>
       </c>
     </row>
-    <row r="785" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A785" s="2">
         <v>2240</v>
       </c>
@@ -42913,7 +42916,7 @@
         <v>43.319000000000003</v>
       </c>
     </row>
-    <row r="786" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A786" s="2">
         <v>2239</v>
       </c>
@@ -42966,7 +42969,7 @@
         <v>216.59399999999999</v>
       </c>
     </row>
-    <row r="787" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A787" s="2">
         <v>2238</v>
       </c>
@@ -42997,8 +43000,8 @@
       <c r="M787" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="N787" s="2">
-        <v>4359</v>
+      <c r="N787" s="2" t="s">
+        <v>382</v>
       </c>
       <c r="O787" s="2" t="s">
         <v>57</v>
@@ -43013,7 +43016,7 @@
         <v>52.2</v>
       </c>
     </row>
-    <row r="788" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A788" s="2">
         <v>2237</v>
       </c>
@@ -43066,7 +43069,7 @@
         <v>129.95599999999999</v>
       </c>
     </row>
-    <row r="789" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A789" s="2">
         <v>2230</v>
       </c>
@@ -43119,7 +43122,7 @@
         <v>122.88</v>
       </c>
     </row>
-    <row r="790" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A790" s="2">
         <v>2228</v>
       </c>
@@ -43172,7 +43175,7 @@
         <v>2551.5</v>
       </c>
     </row>
-    <row r="791" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A791" s="2">
         <v>2227</v>
       </c>
@@ -43225,7 +43228,7 @@
         <v>128.80199999999999</v>
       </c>
     </row>
-    <row r="792" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A792" s="2">
         <v>2225</v>
       </c>
@@ -43278,7 +43281,7 @@
         <v>128.80199999999999</v>
       </c>
     </row>
-    <row r="793" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A793" s="2">
         <v>2223</v>
       </c>
@@ -43331,7 +43334,7 @@
         <v>429.26</v>
       </c>
     </row>
-    <row r="794" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A794" s="2">
         <v>2221</v>
       </c>
@@ -43384,7 +43387,7 @@
         <v>2146.2979999999998</v>
       </c>
     </row>
-    <row r="795" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A795" s="2">
         <v>2218</v>
       </c>
@@ -43437,7 +43440,7 @@
         <v>128.77799999999999</v>
       </c>
     </row>
-    <row r="796" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A796" s="2">
         <v>2217</v>
       </c>
@@ -43490,7 +43493,7 @@
         <v>171.70400000000001</v>
       </c>
     </row>
-    <row r="797" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A797" s="2">
         <v>2216</v>
       </c>
@@ -43543,7 +43546,7 @@
         <v>21.463000000000001</v>
       </c>
     </row>
-    <row r="798" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A798" s="2">
         <v>2215</v>
       </c>
@@ -43596,7 +43599,7 @@
         <v>42.926000000000002</v>
       </c>
     </row>
-    <row r="799" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A799" s="2">
         <v>2214</v>
       </c>
@@ -43627,8 +43630,8 @@
       <c r="M799" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="N799" s="2">
-        <v>4359</v>
+      <c r="N799" s="2" t="s">
+        <v>382</v>
       </c>
       <c r="O799" s="2" t="s">
         <v>57</v>
@@ -43643,7 +43646,7 @@
         <v>26.1</v>
       </c>
     </row>
-    <row r="800" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A800" s="2">
         <v>2213</v>
       </c>
@@ -43696,7 +43699,7 @@
         <v>214.63</v>
       </c>
     </row>
-    <row r="801" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A801" s="2">
         <v>2212</v>
       </c>
@@ -43749,7 +43752,7 @@
         <v>42.926000000000002</v>
       </c>
     </row>
-    <row r="802" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A802" s="2">
         <v>2211</v>
       </c>
@@ -43802,7 +43805,7 @@
         <v>42.926000000000002</v>
       </c>
     </row>
-    <row r="803" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A803" s="2">
         <v>2210</v>
       </c>
@@ -43855,7 +43858,7 @@
         <v>128.77799999999999</v>
       </c>
     </row>
-    <row r="804" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A804" s="2">
         <v>2209</v>
       </c>
@@ -43886,8 +43889,8 @@
       <c r="M804" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="N804" s="2">
-        <v>4359</v>
+      <c r="N804" s="2" t="s">
+        <v>382</v>
       </c>
       <c r="O804" s="2" t="s">
         <v>57</v>
@@ -43902,7 +43905,7 @@
         <v>26.1</v>
       </c>
     </row>
-    <row r="805" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A805" s="2">
         <v>2208</v>
       </c>
@@ -43955,7 +43958,7 @@
         <v>42.926000000000002</v>
       </c>
     </row>
-    <row r="806" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A806" s="2">
         <v>2207</v>
       </c>
@@ -44008,7 +44011,7 @@
         <v>256.24299999999999</v>
       </c>
     </row>
-    <row r="807" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A807" s="2">
         <v>2206</v>
       </c>
@@ -44061,7 +44064,7 @@
         <v>85.414000000000001</v>
       </c>
     </row>
-    <row r="808" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A808" s="2">
         <v>2205</v>
       </c>
@@ -44114,7 +44117,7 @@
         <v>42.707000000000001</v>
       </c>
     </row>
-    <row r="809" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A809" s="2">
         <v>2204</v>
       </c>
@@ -44161,7 +44164,7 @@
         <v>102.4</v>
       </c>
     </row>
-    <row r="810" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A810" s="2">
         <v>2203</v>
       </c>
@@ -44208,7 +44211,7 @@
         <v>102.4</v>
       </c>
     </row>
-    <row r="811" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A811" s="2">
         <v>2202</v>
       </c>
@@ -44261,7 +44264,7 @@
         <v>213.536</v>
       </c>
     </row>
-    <row r="812" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A812" s="2">
         <v>2201</v>
       </c>
@@ -44314,7 +44317,7 @@
         <v>42.707000000000001</v>
       </c>
     </row>
-    <row r="813" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A813" s="2">
         <v>2200</v>
       </c>
